--- a/polymercanon/Paper-Results/Excel/Validation/Duration.xlsx
+++ b/polymercanon/Paper-Results/Excel/Validation/Duration.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,11 +456,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](CC)(CC)O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -474,11 +474,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C)(C)O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -492,11 +492,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{[][&gt;]C/C=C\C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -510,11 +510,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -528,11 +528,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc1)ccc1)(C)O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -546,11 +546,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(COCCCCCC)[&lt;],[&gt;]OC(COCCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -564,11 +564,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -582,11 +582,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C)(C)N[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -600,11 +600,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(CCCC)C[&lt;],[&gt;]CC(CCCC)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -618,11 +618,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCCCCCCCC)[&lt;],[&gt;]C(OCCCCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -636,11 +636,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(COCCCC)[&lt;],[&gt;]OC(COCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -654,11 +654,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -672,11 +672,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -690,11 +690,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(CCC)C[&lt;],[&gt;]CC(CCC)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -708,11 +708,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCCCCCCCCCC)[&lt;],[&gt;]C(OCCCCCCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -726,11 +726,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(CC)C[&lt;],[&gt;]CC(CC)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -744,11 +744,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](CCC(F)(F)F)(C)O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -762,11 +762,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -780,11 +780,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C)(C)CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -798,11 +798,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCCCCCCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -816,11 +816,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;],[&gt;]CC=C(C)C[&lt;],[&gt;]CC(C)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -834,11 +834,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCCCCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -852,11 +852,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCCCO[&lt;1],[&gt;3]C(=O)CCCCC(=O)[&lt;2],[&gt;2]OCCCCO[&lt;3],[&gt;3]C(=O)CCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -870,11 +870,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -888,11 +888,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(C)[&lt;],[&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -906,11 +906,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCCCCC)[&lt;],[&gt;]C(OCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -924,11 +924,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCC(CCCC)CC)[&lt;],[&gt;]C(OCC(CCCC)CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -942,11 +942,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCCCCCCCC)=O)[&lt;],[&gt;]C(C(OCCCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -960,11 +960,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCCCCCC)[&lt;],[&gt;]C(OCCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -978,11 +978,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(OC)[&lt;],[&gt;]OC(OC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -996,11 +996,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(C)C(C=C)[&lt;],[&gt;]C(C=C)C(C)[&lt;],[&gt;]CC=CC(C)[&lt;],[&gt;]C(C)C=CC[&lt;],[&gt;]CC(C=CC)[&lt;],[&gt;]C(C=CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1014,11 +1014,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCCCCCCC)=O)[&lt;],[&gt;]C(C(OCCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1050,11 +1050,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCCCCCCCCC)=O)[&lt;],[&gt;]C(C(OCCCCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCCCCCC)=O)[&lt;],[&gt;]C(C(OCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CCCCC(=O)[&lt;1],[&gt;3]OCCCCCCCCCCO[&lt;2],[&gt;2]C(=O)CCCCC(=O)[&lt;3],[&gt;3]OCCCCCCCCCCO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1104,11 +1104,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{[][&gt;]OC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1122,11 +1122,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCCCCCCCCCCC)=O)[&lt;],[&gt;]C(C)(C(OCCCCCCCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCCCC)=O)[&lt;],[&gt;]C(C(OCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1158,11 +1158,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CCCCC)[&lt;],[&gt;]C(CCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCC(C)CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1194,11 +1194,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCCCC)[&lt;],[&gt;]C(OCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1212,11 +1212,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(C(C)C)C[&lt;],[&gt;]CC(C(C)C)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CCCC)[&lt;],[&gt;]C(CCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1248,11 +1248,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CCC)[&lt;],[&gt;]C(CCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(Cl)C[&lt;],[&gt;]CC(Cl)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{[][&gt;]SCC(C)[&lt;],[&gt;]SC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1302,11 +1302,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)CCCCCCCC(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)CCCCCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OC(CCCCCC)C)=O)[&lt;],[&gt;]C(C(OC(CCCCCC)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCCC)=O)[&lt;],[&gt;]C(C(OCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1374,11 +1374,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)[&lt;],[&gt;]C(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1392,11 +1392,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(F)(F)[&lt;],[&gt;]C(F)(F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1410,11 +1410,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)CCCCC(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)CCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1428,11 +1428,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OC(CCCCC)C)=O)[&lt;],[&gt;]C(C(OC(CCCCC)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CCCC(C)C)[&lt;],[&gt;]C(CCCC(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1464,11 +1464,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{[][&gt;]OC(C)CCCC(C)C(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1482,11 +1482,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(Br)C[&lt;],[&gt;]CC(Br)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1500,11 +1500,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)CCCCCCCCC(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)CCCCCCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc1)ccc1)(C)CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCC(C)C)=O)[&lt;],[&gt;]C(C(OCC(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1554,11 +1554,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCC(C)C)[&lt;],[&gt;]C(OCC(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1572,11 +1572,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OCC)=O)[&lt;],[&gt;]C(C(OCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCCCCCCC)=O)[&lt;],[&gt;]C(C)(C(OCCCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1608,11 +1608,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(CC)C)[&lt;],[&gt;]C(OC(CC)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OC(CC)C)=O)[&lt;],[&gt;]C(C(OC(CC)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCC)[&lt;],[&gt;]C(OCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1662,11 +1662,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(nc(C)n1)nc1C(F)(C(F)(F)F)OC(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)OC(C(F)(F)F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1680,11 +1680,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(Cl)[&lt;],[&gt;]C(Cl)(Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OC(CC)CC)=O)[&lt;],[&gt;]C(C(OC(CC)CC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CCC(C)C)[&lt;],[&gt;]C(CCC(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1734,11 +1734,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(nc(C(F)(F)F)n1)nc1C(C(F)(F)F)OC(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)C(F)(F)OC(C(F)(F)F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1752,11 +1752,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(CCl)(CCl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1770,11 +1770,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C)(c(cc1)ccc1N(C)C)CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1788,11 +1788,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCCCCC)=O)[&lt;],[&gt;]C(C)(C(OCCCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1806,11 +1806,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C=C)[&lt;],[&gt;]C(C=C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1824,11 +1824,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(C)C)[&lt;],[&gt;]C(OC(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1842,11 +1842,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)CCC(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)CCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1860,11 +1860,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(SC)[&lt;],[&gt;]C(SC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc2)ccc2)(c(cc2)ccc2)O[Si](C)(C)c(cc1)ccc1[Si](C)(C)O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1896,11 +1896,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(CCC)=O)[&lt;],[&gt;]C(OC(CCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1914,11 +1914,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2COCCCCCC)[&lt;],[&gt;]C(c(cc1)ccc1COCCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2CCCC)[&lt;],[&gt;]C(c(cc1)ccc1CCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1950,11 +1950,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OC)=O)[&lt;],[&gt;]C(C(OC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1968,11 +1968,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(CC)=O)[&lt;],[&gt;]C(OC(CC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1986,11 +1986,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCC(CC)CC)=O)[&lt;],[&gt;]C(C)(C(OCC(CC)CC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -2004,11 +2004,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2)c(c2)OCCCCCCCC)[&lt;],[&gt;]C(c(ccc1)c(c1)OCCCCCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2022,11 +2022,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=C(C(C)(C)C)C[&lt;],[&gt;]CC(C(C)(C)C)=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2040,11 +2040,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCCC)=O)[&lt;],[&gt;]C(C)(C(OCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2076,11 +2076,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2COCCC)[&lt;],[&gt;]C(c(cc1)ccc1COCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2094,11 +2094,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(cc1)cc(CC)c1C[&lt;],[&gt;]Cc(c(c2)CC)ccc2C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2112,11 +2112,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(F)(F)F)[&lt;],[&gt;]C(C(F)(F)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -2130,11 +2130,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(C)=O)[&lt;],[&gt;]C(OC(C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2148,11 +2148,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CC(C)C)[&lt;],[&gt;]C(CC(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -2166,11 +2166,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC=O)[&lt;],[&gt;]C(OC=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2184,11 +2184,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(=O)CCl)[&lt;],[&gt;]C(OC(=O)CCl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -2202,11 +2202,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCC(C)(C)C)=O)[&lt;],[&gt;]C(C)(C(OCC(C)(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -2220,11 +2220,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCC)=O)[&lt;],[&gt;]C(C)(C(OCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCCCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc1)ccc1C)(c(cc1)ccc1C)CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2274,11 +2274,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{[][&gt;2]NCCCCCCN[&lt;1],[&gt;3]C(=O)CCCCCCCCC(=O)[&lt;2],[&gt;2]NCCCCCCN[&lt;3],[&gt;3]C(=O)CCCCCCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2292,11 +2292,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CCC(CC2)CCC2)[&lt;],[&gt;]C(CCC(CC1)CCC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2310,11 +2310,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(C(F)(F)F)(F)F)[&lt;],[&gt;]C(C(C(F)(F)F)(F)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2328,11 +2328,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2346,11 +2346,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C(OC(C)(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2364,11 +2364,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(COc(cc2)ccc2)[&lt;],[&gt;]OC(COc(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2382,11 +2382,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(F)(C(F)(F)F)[&lt;],[&gt;]C(F)(C(F)(F)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2400,11 +2400,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2418,11 +2418,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(ccc1)cc1O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2436,11 +2436,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCCC(C)(C)C)=O)[&lt;],[&gt;]C(C)(C(OCCC(C)(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2454,11 +2454,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CCCCCCCCC(=O)[&lt;1],[&gt;3]NCCCCCCCCCCN[&lt;2],[&gt;2]C(=O)CCCCCCCCC(=O)[&lt;3],[&gt;3]NCCCCCCCCCCN[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2472,11 +2472,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(NCCCC)=O)[&lt;],[&gt;]C(C(NCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2490,11 +2490,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(C(F)(F)F)=O)[&lt;],[&gt;]C(OC(C(F)(F)F)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2508,11 +2508,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2OCCCC)[&lt;],[&gt;]C(c(cc1)ccc1OCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2526,11 +2526,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(CC(C)C)=O)[&lt;],[&gt;]C(C)(C(CC(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2544,11 +2544,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2562,11 +2562,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2580,11 +2580,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(CCC)O1)CC1[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2616,11 +2616,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)c(ccc1)cc1C(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)c(ccc1)cc1C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2634,11 +2634,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCC)=O)[&lt;],[&gt;]C(C)(C(OCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2652,11 +2652,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc1)ccc1)(c(cc1)ccc1N(C)C)CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2670,11 +2670,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OC(C)C)=O)[&lt;],[&gt;]C(C)(C(OC(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2688,11 +2688,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(cc1)cc(C)c1C[&lt;],[&gt;]Cc(c(c2)C)ccc2C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2706,11 +2706,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC(C(C)C)O1)CC1[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -2724,11 +2724,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(C(OCCCC)=O)[&lt;],[&gt;]C(Cl)(C(OCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2742,11 +2742,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -2760,11 +2760,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OC(CC)C)=O)[&lt;],[&gt;]C(C)(C(OC(CC)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CCCCC(=O)[&lt;1],[&gt;3]NCCCCCCN[&lt;2],[&gt;2]C(=O)CCCCC(=O)[&lt;3],[&gt;3]NCCCCCCN[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2796,11 +2796,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2OCCC(C)C)[&lt;],[&gt;]C(c(cc1)ccc1OCCC(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -2814,11 +2814,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(C(C(F)(F)F)(F)F)(F)F)[&lt;],[&gt;]C(C(C(C(F)(F)F)(F)F)(F)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -2832,11 +2832,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc2)ccc2)(c(cc2)ccc2)c(ccc1)cc1O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2850,11 +2850,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(cc1)ccc1C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -2868,11 +2868,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CC(CC2)CC2)[&lt;],[&gt;]C(CC(CC1)CC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -2886,11 +2886,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cc(cc2)ccc2)[&lt;],[&gt;]C(Cc(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -2904,11 +2904,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCCCCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -2922,11 +2922,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)c(c(c1cc2)cc2)ccc1C(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)c(c(c1cc2)cc2)ccc1C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -2940,11 +2940,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2OCCC)[&lt;],[&gt;]C(c(cc1)ccc1OCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -2958,11 +2958,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(C(OCCC)=O)[&lt;],[&gt;]C(Cl)(C(OCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -2976,11 +2976,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)c(ccc1)c(cc2)c1c(c2)C(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)c(ccc1)c(cc2)c1c(c2)C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -2994,11 +2994,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OC1CC)C(O1)C[&lt;],[&gt;]CC(OC(CC)O2)CC2[&lt;],[&gt;]C(OC(CC)O4)CC4C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -3012,11 +3012,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)c(cc1)ccc1C(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)c(cc1)ccc1C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -3030,11 +3030,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(C(OC(CC)C)=O)[&lt;],[&gt;]C(Cl)(C(OC(CC)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -3048,11 +3048,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)[&lt;],[&gt;]C(Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -3066,11 +3066,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(CC(CC2)CCC2)[&lt;],[&gt;]C(CC(CC1)CCC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -3084,11 +3084,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(CC2)CC2)[&lt;],[&gt;]C(C(CC1)CC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -3102,11 +3102,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OCC(C)O)=O)[&lt;],[&gt;]C(C)(C(OCC(C)O)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -3120,11 +3120,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2COC)[&lt;],[&gt;]C(c(cc1)ccc1COC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -3138,11 +3138,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(cc1)cc(Cl)c1C[&lt;],[&gt;]Cc(c(c2)Cl)ccc2C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -3156,11 +3156,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(cc1)cc(Br)c1C[&lt;],[&gt;]Cc(c(c2)Br)ccc2C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -3174,11 +3174,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCCOc(cc1)ccc1C(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -3192,11 +3192,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(O)[&lt;],[&gt;]C(O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -3210,11 +3210,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(cc1)ccc1O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -3228,11 +3228,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2C(CC)C)[&lt;],[&gt;]C(c(cc1)ccc1C(CC)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -3246,11 +3246,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2OCC)[&lt;],[&gt;]C(c(cc1)ccc1OCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -3264,11 +3264,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)OCCO)(C)[&lt;],[&gt;]C(C(=O)OCCO)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -3282,11 +3282,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(cc1)ccc1S[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -3300,11 +3300,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2C(C)C)[&lt;],[&gt;]C(c(cc1)ccc1C(C)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc(c2)C(C)(C)C)c(c2)C)[&lt;],[&gt;]C(c(cc(c1)C(C)(C)C)c(c1)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -3336,11 +3336,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2OC)[&lt;],[&gt;]C(c(cc1)ccc1OC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -3354,11 +3354,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(C(OC(C)C)=O)[&lt;],[&gt;]C(Cl)(C(OC(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -3372,11 +3372,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(c(C)c2)ccc2OC)[&lt;],[&gt;]C(c(c(C)c1)ccc1OC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -3390,11 +3390,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(CC2)CCC2)[&lt;],[&gt;]C(C(CC1)CCC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -3408,11 +3408,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(cc1)cc(C#N)c1C[&lt;],[&gt;]Cc(c(c2)C#N)ccc2C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(F)(F)c(cc1)ccc1C(F)(F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -3444,11 +3444,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CCCCC(=O)[&lt;1],[&gt;3]NCc(ccc1)cc1CN[&lt;2],[&gt;2]C(=O)CCCCC(=O)[&lt;3],[&gt;3]NCc(ccc1)cc1CN[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -3462,11 +3462,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2Cl)ccc2)[&lt;],[&gt;]C(c(cc1Cl)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -3480,11 +3480,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)OCCCl)(C)[&lt;],[&gt;]C(C(=O)OCCCl)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(C(OCC)=O)[&lt;],[&gt;]C(Cl)(C(OCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -3516,11 +3516,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C(CC1)CCC1)(C)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -3534,11 +3534,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)c(cc2)ccc2C(=O)[&lt;1],[&gt;3]OCC(CC1)CCC1CO[&lt;2],[&gt;2]C(=O)c(cc2)ccc2C(=O)[&lt;3],[&gt;3]OCC(CC1)CCC1CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -3552,11 +3552,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2C)ccc2)[&lt;],[&gt;]C(c(cc1C)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -3570,11 +3570,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{[][&gt;]Cc(c(c1)C)cc(C)c1C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -3588,11 +3588,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(Cl)(F)C(F)(F)[&lt;],[&gt;]C(F)(F)C(Cl)(F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -3606,11 +3606,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -3624,11 +3624,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2C)[&lt;],[&gt;]C(c(cc1)ccc1C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -3642,11 +3642,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2F)c(cc2)F)[&lt;],[&gt;]C(c(cc1F)c(cc1)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -3660,11 +3660,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2)c(c2)CC)[&lt;],[&gt;]C(c(ccc1)c(c1)CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -3678,11 +3678,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2C)cc(c2)C)[&lt;],[&gt;]C(c(cc1C)cc(c1)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -3696,11 +3696,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)OC(CC2)CCC2)(C)[&lt;],[&gt;]C(C(=O)OC(CC1)CCC1)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(nc2)ccc2)[&lt;],[&gt;]C(c(nc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -3732,11 +3732,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -3750,11 +3750,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C#N)[&lt;],[&gt;]C(C#N)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(OCO1)CC1[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -3786,11 +3786,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2)c(c2)F)[&lt;],[&gt;]C(c(ccc1)c(c1)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -3804,11 +3804,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(c(F)c2F)c(c(c2F)F)F)[&lt;],[&gt;]C(c(c(F)c1F)c(c(c1F)F)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -3822,11 +3822,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -3840,11 +3840,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2F)[&lt;],[&gt;]C(c(cc1)ccc1F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -3858,11 +3858,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C)(C(OC(C)(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -3876,11 +3876,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2C)ccc2C)[&lt;],[&gt;]C(c(cc1C)ccc1C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -3894,11 +3894,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2C)c(cc2)F)[&lt;],[&gt;]C(c(cc1C)c(cc1)F)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -3912,11 +3912,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(c(C)c2)ccc2C)[&lt;],[&gt;]C(c(c(C)c1)ccc1C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -3930,11 +3930,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2C(OC)=O)[&lt;],[&gt;]C(c(cc1)ccc1C(OC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -3948,11 +3948,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)cc(C)c2Cl)[&lt;],[&gt;]C(c(cc1)cc(C)c1Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -3966,11 +3966,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)(C(=O)OC(CC2)CCC2)[&lt;],[&gt;]C(Cl)(C(=O)OC(CC1)CCC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -3984,11 +3984,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{[][&gt;2]NCc(cc1)ccc1CN[&lt;1],[&gt;3]C(=O)CCCCCCCCC(=O)[&lt;2],[&gt;2]NCc(cc1)ccc1CN[&lt;3],[&gt;3]C(=O)CCCCCCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -4002,11 +4002,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2Sc(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2Sc(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -4020,11 +4020,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2Cl)[&lt;],[&gt;]C(c(cc1)ccc1Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -4038,11 +4038,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(nc(C(C(OC(F)(F)F)(F)F)(F)F)n1)nc1C(F)(F)C(F)(F)C(F)(F)C(F)(F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -4056,11 +4056,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](c(cc1)ccc1)(C)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -4074,11 +4074,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2)c(c2)Cl)[&lt;],[&gt;]C(c(ccc1)c(c1)Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -4092,11 +4092,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)C)ccc2C(C)(CC)c(cc1)cc(C)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)C)ccc2C(C)(CC)c(cc1)cc(C)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -4110,11 +4110,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2Cl)c(cc2)Cl)[&lt;],[&gt;]C(c(cc1Cl)c(cc1)Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)Oc(cc2)ccc2)(C)[&lt;],[&gt;]C(C(=O)Oc(cc1)ccc1)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C#N)(C)[&lt;],[&gt;]C(C#N)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -4164,11 +4164,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(c(cc2)ccc2C)[&lt;],[&gt;]C(C)(c(cc1)ccc1C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -4182,11 +4182,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)cc(F)c2Cl)[&lt;],[&gt;]C(c(cc1)cc(F)c1Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -4200,11 +4200,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(CCC)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(CCC)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -4218,11 +4218,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;3]C(=O)c(cc1)cc(c1c1)ccc1C(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)c(cc1)cc(c1c1)ccc1C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -4236,11 +4236,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2CO)ccc2)[&lt;],[&gt;]C(c(cc1CO)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -4254,11 +4254,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2Cl)ccc2Cl)[&lt;],[&gt;]C(c(cc1Cl)ccc1Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -4272,11 +4272,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{[][&gt;2]CC[&lt;1],[&gt;3]N(C(c%12cc%13)=O)C(=O)c%12cc%13Oc(cc6)ccc6Oc(cc3)ccc3Oc(ccc1C2=O)cc1C(=O)N2[&lt;2],[&gt;2]CC[&lt;3],[&gt;3]N(C(c%12cc%13)=O)C(=O)c%12cc%13Oc(cc6)ccc6Oc(cc3)ccc3Oc(ccc%12C%13=O)cc%12C(=O)N%13[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -4290,11 +4290,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{[][&gt;2]NCCCCCCN[&lt;1],[&gt;3]C(=O)c(ccc1)cc1C(=O)[&lt;2],[&gt;2]NCCCCCCN[&lt;3],[&gt;3]C(=O)c(ccc1)cc1C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -4308,11 +4308,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -4326,11 +4326,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(c(Cl)c2)ccc2Cl)[&lt;],[&gt;]C(c(c(Cl)c1)ccc1Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -4344,11 +4344,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C)(CC)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C)(CC)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -4362,11 +4362,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2)c(c2)C)[&lt;],[&gt;]C(c(ccc1)c(c1)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -4380,11 +4380,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2)(C)[&lt;],[&gt;]C(c(cc1)ccc1)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -4398,11 +4398,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C)(CCC)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C)(CCC)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -4416,11 +4416,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Nc(ccc1)cc1N[&lt;1],[&gt;3]C(=O)c(ccc2)cc2C(=O)[&lt;2],[&gt;2]Nc(ccc1)cc1N[&lt;3],[&gt;3]C(=O)c(ccc2)cc2C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -4434,11 +4434,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2-c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1-c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -4452,11 +4452,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(C)c(cc1)cc(C)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c8)C)ccc8C(C)(C)c(cc4)cc(Cl)c4O[&lt;2],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(C)c(cc1)cc(C)c1O[&lt;1],[&gt;3]Oc(c(c8)C)ccc8C(C)(C)c(cc4)cc(Cl)c4O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -4470,11 +4470,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2CO)[&lt;],[&gt;]C(c(cc1)ccc1CO)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccn2)[&lt;],[&gt;]C(c(cc1)ccn1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -4506,11 +4506,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(CC)c(cc1)cc(Cl)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(CC)c(cc1)cc(Cl)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -4524,11 +4524,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2C)c(cc2)C)[&lt;],[&gt;]C(c(cc1C)c(cc1)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -4542,11 +4542,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2)ccc2Br)[&lt;],[&gt;]C(c(cc1)ccc1Br)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -4560,11 +4560,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2Cl)c(c2)C)[&lt;],[&gt;]C(c(ccc1Cl)c(c1)C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -4578,11 +4578,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(N(CC2)C(C2)=O)[&lt;],[&gt;]C(N(CC1)C(C1)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -4596,11 +4596,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc2Cl)cc(Cl)c2Cl)[&lt;],[&gt;]C(c(cc1Cl)cc(Cl)c1Cl)C[&lt;],[&gt;]CC(c(c(Cl)c4)c(cc4Cl)Cl)[&lt;],[&gt;]C(c(c(Cl)c%16)c(cc%16Cl)Cl)C[&lt;],[&gt;]CC(c(cc8Cl)c(c(c8)Cl)Cl)[&lt;],[&gt;]C(c(cc%16Cl)c(c(c%16)Cl)Cl)C[&lt;],[&gt;]CC(c(c(Cl)c%16Cl)ccc%16Cl)[&lt;],[&gt;]C(c(c(Cl)c%16Cl)ccc%16Cl)C[&lt;],[&gt;]CC(c(c(c%16Cl)Cl)c(cc%16)Cl)[&lt;],[&gt;]C(c(c(c%16Cl)Cl)c(cc%16)Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -4614,11 +4614,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc8)ccc8C(C)(C)c(cc4)cc(Cl)c4O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(C)c(cc1)ccc1O[&lt;2],[&gt;3]Oc(cc8)ccc8C(C)(C)c(cc4)cc(Cl)c4O[&lt;1],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -4632,11 +4632,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(C)c(cc1)cc(Cl)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)Cl)ccc2C(C)(C)c(cc1)cc(Cl)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -4650,11 +4650,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Oc(cc1)ccc1O[&lt;1],[&gt;3]c(cc4)ccc4C(=O)c(cc2)ccc2[&lt;2],[&gt;2]Oc(cc1)ccc1O[&lt;3],[&gt;3]c(cc4)ccc4C(=O)c(cc8)ccc8[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -4668,11 +4668,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2Cc(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2Cc(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -4686,11 +4686,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>{[][&gt;]Oc(cc1)ccc1C(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -4704,11 +4704,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(CCC)(CCC)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(CCC)(CCC)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -4722,11 +4722,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C(C)C)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C(C)C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -4740,11 +4740,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C)(C)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C)(C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -4758,11 +4758,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(n(c(ccc3)c4c3)c(c4c3)ccc3)[&lt;],[&gt;]C(n(c(ccc1)c2c1)c(c2c1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -4776,11 +4776,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc3)cc(ccc4)c3c4)[&lt;],[&gt;]C(c(cc1)cc(ccc2)c1c2)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -4794,11 +4794,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(F)(F)C(F)(C(F)(F)F)[&lt;],[&gt;]C(F)(C(F)(F)F)C(F)(F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -4812,11 +4812,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(=C(Cl)Cl)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(=C(Cl)Cl)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -4830,11 +4830,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc3)c(ccc4)c(c4)c3)[&lt;],[&gt;]C(c(cc1)c(ccc2)c(c2)c1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -4848,11 +4848,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(ccc2)c(c2)CO)[&lt;],[&gt;]C(c(ccc1)c(c1)CO)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -4866,11 +4866,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C#N)(C(OC)=O)[&lt;],[&gt;]C(C#N)(C(OC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -4884,11 +4884,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc4)ccc4C(CC2)(CC2)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc4)ccc4C(CC2)(CC2)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -4902,11 +4902,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)c(cc4)ccc4C(=O)[&lt;1],[&gt;3]Oc(c(c2)C)ccc2C(C)(C)c(cc1)cc(C)c1O[&lt;2],[&gt;2]C(=O)c(cc4)ccc4C(=O)[&lt;3],[&gt;3]Oc(c(c2)C)ccc2C(C)(C)c(cc1)cc(C)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -4920,11 +4920,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc4)ccc4C(CCC2)(CC2)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc4)ccc4C(CCC2)(CC2)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -4938,11 +4938,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C(F)(F)F)(C(F)(F)F)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C(F)(F)F)(C(F)(F)F)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc4)ccc4C(Cc(cc2)ccc2)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc4)ccc4C(Cc(cc2)ccc2)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -4974,11 +4974,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C(F)(F)Cl)(C(F)(F)Cl)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C(F)(F)Cl)(C(F)(F)Cl)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -4992,11 +4992,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc8)ccc8S(=O)(=O)c(cc%16)ccc%16[&lt;1],[&gt;3]Oc(cc2)ccc2C(C)(C)c(cc1)ccc1O[&lt;2],[&gt;2]c(cc8)ccc8S(=O)(=O)c(cc4)ccc4[&lt;3],[&gt;3]Oc(cc2)ccc2C(C)(C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -5010,11 +5010,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc8)ccc8C(C)(C)c(cc4Cl)cc(Cl)c4O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)Cl)c(Cl)cc2C(C)(C)c(cc1)ccc1O[&lt;2],[&gt;3]Oc(cc8)ccc8C(C)(C)c(cc4Cl)cc(Cl)c4O[&lt;1],[&gt;3]Oc(c(c2)Cl)c(Cl)cc2C(C)(C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -5028,11 +5028,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(F)(F)C(F)(c(c(F)c2F)c(c(c2F)F)F)[&lt;],[&gt;]C(F)(c(c(F)c1F)c(c(c1F)F)F)C(F)(F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -5046,11 +5046,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)C)c(C)cc2C(C)(C)c(cc1C)cc(C)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)C)c(C)cc2C(C)(C)c(cc1C)cc(C)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -5064,11 +5064,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc2)cc2C(=O)c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(ccc2)cc2C(=O)c(ccc%18)cc%18[&lt;3],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -5082,11 +5082,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(F)(F)C(c(cc2)ccc2)(F)[&lt;],[&gt;]C(c(cc1)ccc1)(F)C(F)(F)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -5100,11 +5100,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)c(cc4)ccc4C(=O)[&lt;1],[&gt;3]Oc(cc2)ccc2C(C)(C)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)c(cc4)ccc4C(=O)[&lt;3],[&gt;3]Oc(cc2)ccc2C(C)(C)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -5118,11 +5118,11 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(cc1C)cc(C)c1O[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -5136,11 +5136,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10Sc(cc5)ccc5Oc(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(ccc%10)cc%10[&lt;3],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10Sc(cc5)ccc5Oc(ccc%10C%11=O)cc%10C(=O)N%11[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -5154,11 +5154,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc%18)ccc%18C(=O)c(cc%18)c(cc%18)[&lt;1],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(cc%18)ccc%18C(=O)c(cc%18)c(cc%18)[&lt;3],[&gt;2]c(cc2)c(cc2)C(=O)c(cc%18)ccc%18[&lt;3],[&gt;2]c(cc2)c(cc2)C(=O)c(cc1)ccc1[&lt;1],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -5172,11 +5172,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2C(=O)c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(cc2)ccc2C(=O)c(ccc%18)cc%18[&lt;3],[&gt;2]c(ccc%18)cc%18C(=O)c(cc%18)ccc%18[&lt;3],[&gt;2]c(ccc%18)cc%18C(=O)c(cc%18)ccc%18[&lt;1],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -5190,11 +5190,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>{[][&gt;]Oc(cc1-c(cc2)ccc2)cc(-c(cc2)ccc2)c1[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -5208,11 +5208,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Oc(cc1)ccc1O[&lt;1],[&gt;3]c(cc4)ccc4S(=O)(=O)c(cc2)ccc2[&lt;2],[&gt;2]Oc(cc1)ccc1O[&lt;3],[&gt;3]c(cc4)ccc4S(=O)(=O)c(cc8)ccc8[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -5226,11 +5226,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc8)ccc8S(=O)(=O)c(cc%16)ccc%16[&lt;1],[&gt;3]Oc(cc2)ccc2S(=O)(=O)c(cc1)ccc1O[&lt;2],[&gt;2]c(cc8)ccc8S(=O)(=O)c(cc4)ccc4[&lt;3],[&gt;3]Oc(cc2)ccc2S(=O)(=O)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -5244,11 +5244,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10C(C)(C)c(cc5)ccc5Oc(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(ccc%10)cc%10[&lt;3],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10C(C)(C)c(cc5)ccc5Oc(ccc%10C%11=O)cc%10C(=O)N%11[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -5262,11 +5262,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2C(=O)c(cc1)ccc1[&lt;1],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(cc2)ccc2C(=O)c(cc%18)ccc%18[&lt;3],[&gt;3]N(C(c%18cc%19)=O)C(=O)c%18cc%19Oc(cc%18)ccc%18Sc(cc9)ccc9Oc(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -5280,11 +5280,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>{[][&gt;2]n(c(c%17cc%18c%19=O)=O)c(=O)c%17cc%18c(=O)n%19[&lt;1],[&gt;3]c(ccc4)cc4Oc(ccc2)cc2Oc(ccc%17)cc%17[&lt;2],[&gt;2]n(c(c8cc9c%10=O)=O)c(=O)c8cc9c(=O)n%10[&lt;3],[&gt;3]c(ccc4)cc4Oc(ccc2)cc2Oc(ccc1)cc1[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -5298,11 +5298,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)c(cc4)ccc4C(=O)[&lt;1],[&gt;3]Oc(c(c2)C)c(C)cc2C(C)(C)c(cc1C)cc(C)c1O[&lt;2],[&gt;2]C(=O)c(cc4)ccc4C(=O)[&lt;3],[&gt;3]Oc(c(c2)C)c(C)cc2C(C)(C)c(cc1C)cc(C)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -5316,11 +5316,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10Oc(cc5)ccc5Oc(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(ccc%10)cc%10[&lt;3],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10Oc(cc5)ccc5Oc(ccc%10C%11=O)cc%10C(=O)N%11[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -5334,11 +5334,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)Cl)c(Cl)cc2C(C)(C)c(cc1Cl)cc(Cl)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)Cl)c(Cl)cc2C(C)(C)c(cc1Cl)cc(Cl)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -5352,11 +5352,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc5)ccc5C(C(C2)C3)(CC2C3)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc5)ccc5C(C(C2)C3)(CC2C3)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10C(=O)c(cc5)ccc5Oc(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(ccc%10)cc%10[&lt;3],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10C(=O)c(cc5)ccc5Oc(ccc%10C%11=O)cc%10C(=O)N%11[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -5388,11 +5388,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc2)cc2C(=O)c(ccc1)cc1[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(=O)c(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(ccc2)cc2C(=O)c(ccc%18)cc%18[&lt;3],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(=O)c(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -5406,11 +5406,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc6)ccc6C(C(C2)C(C3C4)CC4)(CC23)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc6)ccc6C(C(C2)C(C3C4)CC4)(CC23)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -5424,11 +5424,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10c(cc5)ccc5Oc(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(ccc%10)cc%10[&lt;3],[&gt;3]N(C(c%10cc%11)=O)C(=O)c%10cc%11Oc(cc%10)ccc%10c(cc5)ccc5Oc(ccc%10C%11=O)cc%10C(=O)N%11[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -5442,11 +5442,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(c(c2)Br)c(Br)cc2C(C)(C)c(cc1Br)cc(Br)c1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(c(c2)Br)c(Br)cc2C(C)(C)c(cc1Br)cc(Br)c1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -5460,11 +5460,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc2)cc2C(=O)c(ccc1)cc1[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(ccc2)cc2C(=O)c(ccc%18)cc%18[&lt;3],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -5478,11 +5478,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2Oc(cc1)ccc1[&lt;1],[&gt;3]c(cc(-c(cc%10)ccc%10)c%10cc%11Oc(cc4c(c5)-c(cc6)ccc6)ccc4nc5[&lt;2])nc%10cc%11,[&gt;2]c(cc2)ccc2Oc(cc%10)ccc%10[&lt;3],[&gt;3]c(cc(-c(cc%10)ccc%10)c%10cc%11Oc(cc%10c(c%11)-c(cc%12)ccc%12)ccc%10nc%11[&lt;1])nc%10cc%11[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -5496,11 +5496,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]c(nc%16cc%17)cc(c%16cc%17)c(cc8)ccc8Oc(cc4)ccc4c(c(ccc2)c(c2)n2)cc2[&lt;2],[&gt;2]c(ccc%16)cc%16[&lt;3],[&gt;3]c(nc%16cc%17)cc(c%16cc%17)c(cc8)ccc8Oc(cc4)ccc4c(c(ccc%16)c(c%16)n%16)cc%16[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -5514,11 +5514,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(ccc1)cc1[&lt;1],[&gt;3]c(nc%10cc%11)c(-c(cc%12)ccc%12)c(c%10cc%11)c(cc%10)ccc%10Oc(cc5)ccc5c(c(ccc2)c(c2)n2)c(-c(cc3)ccc3)c2[&lt;2],[&gt;2]c(ccc%10)cc%10[&lt;3],[&gt;3]c(nc%10cc%11)c(-c(cc%12)ccc%12)c(c%10cc%11)c(cc%10)ccc%10Oc(cc5)ccc5c(c(ccc%10)c(c%10)n%10)c(-c(cc%11)ccc%11)c%10[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -5532,11 +5532,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)[&lt;1],[&gt;3]Oc(cc8)ccc8c(cc4)c(cc4)Cc(cc2)c(cc2)c(cc1)ccc1O[&lt;2],[&gt;2]C(=O)[&lt;3],[&gt;3]Oc(cc8)ccc8c(cc4)c(cc4)Cc(cc2)c(cc2)c(cc1)ccc1O[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -5550,11 +5550,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2C(=O)c(ccc1)cc1[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(cc2)ccc2C(=O)c(ccc%18)cc%18[&lt;3],[&gt;2]c(ccc%18)cc%18C(=O)c(cc%18)ccc%18[&lt;3],[&gt;2]c(ccc%18)cc%18C(=O)c(cc%18)ccc%18[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -5568,11 +5568,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc%18)ccc%18C(=O)c(cc%18)c(cc%18)[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(cc%18)ccc%18C(=O)c(cc%18)c(cc%18)[&lt;3],[&gt;2]c(cc2)c(cc2)C(=O)c(cc%18)ccc%18[&lt;3],[&gt;2]c(cc2)c(cc2)C(=O)c(cc1)ccc1[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -5586,11 +5586,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]c(cc(-c(cc6)ccc6)c6cc7Oc(cc2c(c3)-c(cc4)ccc4)ccc2nc3[&lt;2])nc6cc7,[&gt;2]c(cc%13)ccc%13[&lt;3],[&gt;3]c(cc(-c(cc6)ccc6)c6cc7Oc(cc%13c(c%14)-c(cc%15)ccc%15)ccc%13nc%14[&lt;1])nc6cc7[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -5604,11 +5604,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc4)c(cc4)c(cc2)ccc2c(cc1)ccc1[&lt;1],[&gt;3]c(cnc%16cc%17)nc%16cc%17c(cc8)cc(c8n8)nc(c8)[&lt;2],[&gt;2]c(cc4)c(cc4)c(cc2)ccc2c(cc%16)ccc%16[&lt;3],[&gt;2]c(cc%16)ccc%16c(cc%16)ccc%16c(cc%16)c(cc%16)[&lt;3],[&gt;2]c(cc%16)ccc%16c(cc%16)ccc%16c(cc%16)c(cc%16)[&lt;1],[&gt;3]c(cnc%16cc%17)nc%16cc%17c(cc%16)cc(c%16n%16)nc(c%16)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -5622,11 +5622,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]c(cnc4cc5)nc4cc5Oc(cc2)cc(c2n2)nc(c2)[&lt;2],[&gt;2]c(cc9)ccc9[&lt;3],[&gt;3]c(cnc4cc5)nc4cc5Oc(cc%18)cc(c%18n%18)nc(c%18)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -5640,11 +5640,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Oc(cc2)ccc2c(cc1)ccc1O[&lt;1],[&gt;3]C(=O)c(cc%16)ccc%16C(OC8=O)(c(c8c8)ccc8)c(cc4)ccc4C(=O)[&lt;2],[&gt;2]Oc(cc2)ccc2c(cc1)ccc1O[&lt;3],[&gt;3]C(=O)c(cc%16)ccc%16C(OC8=O)(c(c8c8)ccc8)c(cc4)ccc4C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -5658,11 +5658,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2c(cc1)ccc1[&lt;1],[&gt;3]c(cc(-c(cc%10)ccc%10)c%10cc%11Oc(cc4c(c5)-c(cc6)ccc6)ccc4nc5[&lt;2])nc%10cc%11,[&gt;2]c(cc2)ccc2c(cc%10)ccc%10[&lt;3],[&gt;3]c(cc(-c(cc%10)ccc%10)c%10cc%11Oc(cc%10c(c%11)-c(cc%12)ccc%12)ccc%10nc%11[&lt;1])nc%10cc%11[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Oc(cc4)ccc4C(OC2=O)(c(c2c2)ccc2)c(cc1)ccc1O[&lt;1],[&gt;3]C(=O)c(cc%16)ccc%16C(OC%16=O)(c(c%16c%16)ccc%16)c(cc8)ccc8C(=O)[&lt;2],[&gt;2]Oc(cc4)ccc4C(OC2=O)(c(c2c2)ccc2)c(cc1)ccc1O[&lt;3],[&gt;3]C(=O)c(cc%16)ccc%16C(OC%16=O)(c(c%16c%16)ccc%16)c(cc8)ccc8C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -5694,11 +5694,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2C(=O)c(cc1)ccc1[&lt;1],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc4C5=O)cc4C(=O)N5[&lt;2],[&gt;2]c(cc2)ccc2C(=O)c(cc%18)ccc%18[&lt;3],[&gt;3]N(C(c9cc%10)=O)C(=O)c9cc%10C(C(F)(F)F)(C(F)(F)F)c(ccc%18C%19=O)cc%18C(=O)N%19[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -5712,11 +5712,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]c(cnc4cc5)nc4cc5C(=O)c(cc2)cc(c2n2)nc(c2)[&lt;2],[&gt;2]c(cc9)ccc9[&lt;3],[&gt;3]c(cnc4cc5)nc4cc5C(=O)c(cc%18)cc(c%18n%18)nc(c%18)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -5730,11 +5730,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Nc(cc2)ccc2Oc(cc1)ccc1N[&lt;1],[&gt;3]C(=O)c(cc%16)ccc%16C(OC8=O)(c(c8c8)ccc8)c(cc4)ccc4C(=O)[&lt;2],[&gt;2]Nc(cc2)ccc2Oc(cc1)ccc1N[&lt;3],[&gt;3]C(=O)c(cc%16)ccc%16C(OC8=O)(c(c8c8)ccc8)c(cc4)ccc4C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2Oc(cc1)ccc1[&lt;1],[&gt;3]c(nc%16cc%17)cc(c%16cc%17)c(cc%16)ccc%16Oc(cc8)ccc8c(c(ccc4)c(c4)n4)cc4[&lt;2],[&gt;2]c(cc2)ccc2Oc(cc%16)ccc%16[&lt;3],[&gt;3]c(nc%16cc%17)cc(c%16cc%17)c(cc%16)ccc%16Oc(cc8)ccc8c(c(ccc%16)c(c%16)n%16)cc%16[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -5766,11 +5766,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Nc(cc1)ccc1N[&lt;1],[&gt;3]C(=O)c(cc2)ccc2C(=O)[&lt;2],[&gt;2]Nc(cc1)ccc1N[&lt;3],[&gt;3]C(=O)c(cc2)ccc2C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]N(C(c5cc6)=O)C(=O)c5cc6C(=O)c(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(cc%11)ccc%11[&lt;3],[&gt;3]N(C(c5cc6)=O)C(=O)c5cc6C(=O)c(ccc%11C%12=O)cc%11C(=O)N%12[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -5802,11 +5802,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]c(cnc4cc5)nc4cc5S(=O)(=O)c(cc2)cc(c2n2)nc(c2)[&lt;2],[&gt;2]c(cc9)ccc9[&lt;3],[&gt;3]c(cnc4cc5)nc4cc5S(=O)(=O)c(cc%18)cc(c%18n%18)nc(c%18)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -5820,11 +5820,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]N(C(c5cc6)=O)C(=O)c5cc6Oc(ccc2C3=O)cc2C(=O)N3[&lt;2],[&gt;2]c(cc%11)ccc%11[&lt;3],[&gt;3]N(C(c5cc6)=O)C(=O)c5cc6Oc(ccc%11C%12=O)cc%11C(=O)N%12[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -5838,11 +5838,11 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]c(c(-c(cc6)ccc6)c(-c(cc6)ccc6)c6cc7Oc(cc2c(c3-c(cc4)ccc4)-c(cc4)ccc4)ccc2nc3[&lt;2])nc6cc7,[&gt;2]c(cc%13)ccc%13[&lt;3],[&gt;3]c(c(-c(cc6)ccc6)c(-c(cc6)ccc6)c6cc7Oc(cc%13c(c%14-c(cc%15)ccc%15)-c(cc%15)ccc%15)ccc%13nc%14[&lt;1])nc6cc7[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -5856,11 +5856,11 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2c(cc1)ccc1[&lt;1],[&gt;3]c(c(-c(cc%10)ccc%10)c(-c(cc%10)ccc%10)c%10cc%11Oc(cc4c(c5-c(cc6)ccc6)-c(cc6)ccc6)ccc4nc5[&lt;2])nc%10cc%11,[&gt;2]c(cc2)ccc2c(cc%10)ccc%10[&lt;3],[&gt;3]c(c(-c(cc%10)ccc%10)c(-c(cc%10)ccc%10)c%10cc%11Oc(cc%10c(c%11-c(cc%12)ccc%12)-c(cc%12)ccc%12)ccc%10nc%11[&lt;1])nc%10cc%11[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -5874,11 +5874,11 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc1)ccc1[&lt;1],[&gt;3]c(cnc4cc5)nc4cc5c(cc2)cc(c2n2)nc(c2)[&lt;2],[&gt;2]c(cc9)ccc9[&lt;3],[&gt;3]c(cnc4cc5)nc4cc5c(cc%18)cc(c%18n%18)nc(c%18)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -5892,11 +5892,11 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>{[][&gt;2]Nc(cc4)ccc4C(OC2=O)(c(c2c2)ccc2)c(cc1)ccc1N[&lt;1],[&gt;3]C(=O)c(cc%16)ccc%16C(OC%16=O)(c(c%16c%16)ccc%16)c(cc8)ccc8C(=O)[&lt;2],[&gt;2]Nc(cc4)ccc4C(OC2=O)(c(c2c2)ccc2)c(cc1)ccc1N[&lt;3],[&gt;3]C(=O)c(cc%16)ccc%16C(OC%16=O)(c(c%16c%16)ccc%16)c(cc8)ccc8C(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2Oc(cc1)ccc1[&lt;1],[&gt;3]n(c(c4cc5c6=O)=O)c(=O)c4cc5c(=O)n6[&lt;2],[&gt;2]c(cc2)ccc2Oc(cc%10)ccc%10[&lt;3],[&gt;3]n(c(c%10cc%11c%12=O)=O)c(=O)c%10cc%11c(=O)n%12[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -5928,11 +5928,11 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>{[][&gt;]NC(=O)Nc(cc4)ccc4C(NC2=O)(c(c2c2)ccc2)c(cc1)ccc1NC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -5946,11 +5946,11 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(cc2)ccc2C(=O)c(cc1)ccc1[&lt;1],[&gt;3]n(c(c4cc5c6=O)=O)c(=O)c4cc5c(=O)n6[&lt;2],[&gt;2]c(cc2)ccc2C(=O)c(cc%10)ccc%10[&lt;3],[&gt;3]n(c(c%10cc%11c%12=O)=O)c(=O)c%10cc%11c(=O)n%12[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -5964,11 +5964,11 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -5982,11 +5982,11 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>[H]OCCO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D309" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -6000,11 +6000,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>[H]CO{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(=C)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -6018,11 +6018,11 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>[H]CO{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D311" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -6036,11 +6036,11 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}Cl</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -6054,11 +6054,11 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>[H]C(=C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(=C)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D313" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -6072,11 +6072,11 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>[H]CC(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -6090,11 +6090,11 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>ClCC{[&lt;][&gt;]OCC[&lt;][&gt;]}Cl</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D315" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -6108,11 +6108,11 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]C(C)C(=O)O[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D316" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -6126,11 +6126,11 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>[H]c(cc2)c(cc2)C(=S)S{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)(C)C(=O)OCC#C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D317" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -6144,11 +6144,11 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>[H]CC(C#N)(C){[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;];[&gt;]C(C#N)(C)C[H],[&gt;]C=Cc(cc4)c(cc4)[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D318" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -6162,11 +6162,11 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)SC(=S)SCCCCCCCCCCCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D319" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -6180,11 +6180,11 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)SC(=S)S{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}CCCCCCCCCCCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D320" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)SC(=S)S{[&lt;][&gt;]CC(C(NC(C)C)=O)[&lt;],[&gt;]C(C(NC(C)C)=O)C[&lt;][&gt;]}CCCCCCCCCCCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D321" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
@@ -6216,11 +6216,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>[H]C(C2)(O2)C{[&lt;][&gt;]CCO[&lt;][&gt;]}OCC(C1)(O1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -6234,11 +6234,11 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>[H]CC(C)(C){[&lt;][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;][&gt;]}CC(=C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D323" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -6252,11 +6252,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>[H]CC(C)(C){[&lt;][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;][&gt;]}CC(C)CSCCNC(=O)OC(C)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -6270,11 +6270,11 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>[H]NCCSCC(C)C{[&lt;][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;][&gt;]}C(C)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D325" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -6288,11 +6288,11 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>[H]N{[&lt;][&gt;]C(CCC(OCc(cc1)ccc1)=O)C(=O)N[&lt;][&gt;]}CCSCC(C)C{[&lt;][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;][&gt;]}C(C)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -6306,11 +6306,11 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>[H]C(=C)[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C(=C)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D327" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -6324,11 +6324,11 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O{[&lt;][&gt;][Si](C)O[&lt;][&gt;]}[Si](C)(C)O[Si](C)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D328" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -6342,11 +6342,11 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>[H]C[Si](C)(C)O[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D329" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -6360,11 +6360,11 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>[H]NCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCN[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D330" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -6378,11 +6378,11 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>[H]CC(C)(CCC1)N(C1(C)C)O{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;],[&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc4)ccc4)C[&lt;][&gt;]}O[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -6396,11 +6396,11 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]NCCCCCC(=O)[&lt;][&gt;]}O[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D332" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -6414,11 +6414,11 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>[H]OC(=O)CCCC{[&lt;][&gt;]CNC(=O)CCCC[&lt;][&gt;]}C(=O)O[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D333" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -6432,11 +6432,11 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>[H]c(cc1)c(cc1)CO{[&lt;][&gt;]CCO[&lt;],[&gt;]CC(COCCN(C(C)C)C(C)C)O[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D334" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -6450,11 +6450,11 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]NCC(=O)[&lt;],[&gt;]NC(C)C(=O)[&lt;][&gt;]}O[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D335" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -6468,11 +6468,11 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>{[][&gt;]O[Si](C)(C)[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -6486,11 +6486,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC2)CCC2)[&lt;],[&gt;]C(C(CC1)CCC1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -6504,11 +6504,11 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>{[][&gt;]O[Si](C)(C)[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc3C(Oc(cc4)ccc4OCCCC)=O)c(cc3)C(=O)Oc(cc3)ccc3OCCCC)[&lt;],[&gt;]C(c(cc1C(Oc(cc2)ccc2OCCCC)=O)c(cc1)C(=O)Oc(cc1)ccc1OCCCC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D338" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -6522,11 +6522,11 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(C)(C(OCC(CCCC)CC)=O)[&lt;],[&gt;]C(C)(C(OCC(CCCC)CC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -6540,11 +6540,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OCCCC)=O)[&lt;],[&gt;]C(C)(C(OCCCC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -6558,11 +6558,11 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>{[][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D341" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -6576,11 +6576,11 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}{[&lt;][&gt;]C/C=C/C[&lt;],[&gt;]C/C=C\C[&lt;],[&gt;]CC(C=C)[&lt;],[&gt;]C(C=C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D342" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -6594,11 +6594,11 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>{[][&gt;]O[Si](C)(C)[&lt;][&gt;]}{[&lt;][&gt;]C/C=C/C[&lt;],[&gt;]C/C=C\C[&lt;],[&gt;]CC(C=C)[&lt;],[&gt;]C(C=C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>{[][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D344" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -6630,11 +6630,11 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(nc%16)ccc%16)[&lt;],[&gt;]C(c(nc8)ccc8)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccn2)[&lt;],[&gt;]C(c(cc1)ccn1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D345" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -6648,11 +6648,11 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D346" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -6666,11 +6666,11 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D347" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -6684,11 +6684,11 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D348" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -6702,11 +6702,11 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]C(CC)OC[&lt;][&gt;]}COCCOC{[&lt;][&gt;]COC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -6720,11 +6720,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC(CC)[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -6738,11 +6738,11 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>[H]CCC(C){[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -6756,11 +6756,11 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}{[&lt;][&gt;]OC(=O)C(C)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -6774,11 +6774,11 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>{[][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -6792,11 +6792,11 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(c(nc%16)ccc%16)[&lt;],[&gt;]C(c(nc8)ccc8)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D354" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -6810,11 +6810,11 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>[H]CCC(C){[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
@@ -6828,11 +6828,11 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}C(CC)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -6846,11 +6846,11 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C=C)[&lt;],[&gt;]C(C=C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D357" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -6864,11 +6864,11 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]C/C=C/C[&lt;],[&gt;]C/C=C\C[&lt;],[&gt;]CC(C=C)[&lt;],[&gt;]C(C=C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -6882,11 +6882,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC2)CCC2)[&lt;],[&gt;]C(C(CC1)CCC1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -6900,11 +6900,11 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(CC4)CCC4)[&lt;],[&gt;]C(C(CC2)CCC2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D360" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -6918,11 +6918,11 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -6936,11 +6936,11 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>{[][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D362" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="363">
@@ -6954,11 +6954,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(nc%16)ccc%16)[&lt;],[&gt;]C(c(nc8)ccc8)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -6972,11 +6972,11 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]C(C)\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C(C)[&lt;],[&gt;]C(C)/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C(C)[&lt;],[&gt;]C(C)C(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C(C)[&lt;],[&gt;]CC(C)(C=CC)[&lt;],[&gt;]C(C)(C=CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -6990,11 +6990,11 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc%16)ccn%16)[&lt;],[&gt;]C(c(cc8)ccn8)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}CCCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D365" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -7008,11 +7008,11 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>{[][&gt;1]C(C(C4CN5C(C)(C)C)CN(C(C)(C)C)[Sn]5(Cl)Cl)CC4C=C[&lt;1];[H]CC(C)(C)C=C[&lt;1],[H]CC(C)(C)C=CC(CC2)CC2{[&lt;][&gt;]C=CC(CC2)CC2[&lt;][&gt;]}C=C[&lt;1],[&gt;1][H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D366" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -7044,11 +7044,11 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -7062,11 +7062,11 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>{[][&gt;1]C(C(C=2)c3c(c4)OC)C(C(C=2)c3c(c4)OC)C=C[&lt;1];[H]CC(C)(C)[&lt;1],[H]CC(C)(C)C=C{[&lt;][&gt;]C(C(C%12)CO[Si](C)(C)C)CC%12C=C[&lt;][&gt;]}C(C(C6)CO[Si](C)(C)C)CC6[&lt;1],[&gt;1]C=Cc(cc1)c(cc1)[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
@@ -7080,11 +7080,11 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>{[][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]OC(C)C(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -7098,11 +7098,11 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>{[][&gt;]OC(C)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -7116,11 +7116,11 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(nc%16)ccc%16)[&lt;],[&gt;]C(c(nc8)ccc8)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -7134,11 +7134,11 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(nc%16)ccc%16)[&lt;],[&gt;]C(c(nc8)ccc8)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D373" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -7152,11 +7152,11 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(c(cc%16)ccc%16O)[&lt;],[&gt;]C(c(cc8)ccc8O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)(C)[&lt;],[&gt;]C(c(cc1)ccc1)(C)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -7170,11 +7170,11 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;],[&gt;]CC(c(cc4)ccc4S(=O)(=O)O)[&lt;],[&gt;]C(c(cc8)ccc8S(=O)(=O)O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -7188,11 +7188,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -7206,11 +7206,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C(OC(C)(C)C)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -7224,11 +7224,11 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>{[][&gt;][Si](C)(C)O[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -7242,11 +7242,11 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]C(=O)OC(C)CO[&lt;][&gt;]}CC{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -7260,11 +7260,11 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(nc4)ccc4)[&lt;],[&gt;]C(c(nc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOC)=O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -7278,11 +7278,11 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -7296,11 +7296,11 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc%16O)ccc%16O)[&lt;],[&gt;]C(c(cc8O)ccc8O)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -7314,11 +7314,11 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>[H]OCC(=O)O{[&lt;][&gt;]CC(=O)O[&lt;],[&gt;]C(C)C(=O)O[&lt;][&gt;]}C{[&lt;][&gt;]COC[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D383" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -7332,11 +7332,11 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>{[][&gt;]O[Si](C)(C)[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -7350,11 +7350,11 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>{[][&gt;]O[Si](C)(C)[&lt;][&gt;]}{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D385" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -7368,11 +7368,11 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][&gt;]}{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D386" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -7386,11 +7386,11 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -7404,11 +7404,11 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCO[&lt;][&gt;]}{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -7422,11 +7422,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>[H]c(cc2)c(cc2)C(c(cc%16)ccc%16)C{[&lt;][&gt;]CC(c(nc%16)ccc%16)[&lt;],[&gt;]C(c(nc%16)ccc%16)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc8)ccn8)[&lt;],[&gt;]C(c(cc4)ccn4)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -7458,11 +7458,11 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D391" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392">
@@ -7476,11 +7476,11 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>[H]CCC(C){[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]C(C)C(=O)O[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -7494,11 +7494,11 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;][Si](C)(C)O[&lt;][&gt;]}[Si](C)(C){[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394">
@@ -7512,11 +7512,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;][Si](C)(C)O[&lt;][&gt;]}[Si](C)(C){[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -7530,11 +7530,11 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC2)CCC2)[&lt;],[&gt;]C(C(CC1)CCC1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -7548,11 +7548,11 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC2)CCC2)[&lt;],[&gt;]C(C(CC1)CCC1)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -7566,11 +7566,11 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="398">
@@ -7584,11 +7584,11 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -7602,11 +7602,11 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>[H]CCC(C){[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}{[&lt;][&gt;][Si](C)(C)O[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -7620,11 +7620,11 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
     </row>
     <row r="401">
@@ -7638,11 +7638,11 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>{[][&gt;1]CC(c(cc%16)ccc%16)[&lt;1],[&gt;1]C(c(cc%16)ccc%16)C[&lt;1];[H]{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}[&lt;1],[H]O{[&lt;][&gt;]CCO[&lt;][&gt;]}CC{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]C\C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C/C[&lt;],[&gt;]C/C=C(\C)/C[&lt;],[&gt;]C\C(\C)=C\C[&lt;],[&gt;]CC(C(=C)C)[&lt;],[&gt;]C(C(=C)C)C[&lt;],[&gt;]CC(C)(C=C)[&lt;],[&gt;]C(C)(C=C)C[&lt;][&gt;]}[&lt;1],[&gt;1]C(C)CC[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="402">
@@ -7656,11 +7656,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(C(C)C)[&lt;],[&gt;]C(C(C)C)C[&lt;],[&gt;]CCC(C)C[&lt;],[&gt;]CC(C)CC[&lt;],[&gt;]CC(C)(CC)[&lt;],[&gt;]C(C)(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC8)CCC8)[&lt;],[&gt;]C(C(CC%16)CCC%16)C[&lt;][&gt;]}{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC%16)CCC%16)[&lt;],[&gt;]C(C(CC%16)CCC%16)C[&lt;][&gt;]}{[&lt;][&gt;]CCCC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C(CC%16)CCC%16)[&lt;],[&gt;]C(C(CC%16)CCC%16)C[&lt;][&gt;]}C(C)CC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>1686</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="403">
@@ -7674,11 +7674,11 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>[H]CO{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(c(cc2)ccc2){[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc4)ccc4)C[&lt;][&gt;]}SC(=S)c(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="404">
@@ -7692,11 +7692,11 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]CC(C(=O)OCCO)[&lt;],[&gt;]C(C(=O)OCCO)C[&lt;][&gt;]}C(c(cc2)ccc2)(c(cc2)ccc2)C{[&lt;][&gt;][Si](CC)(CC)CCC[&lt;][&gt;]}c(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="405">
@@ -7710,11 +7710,11 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc2)ccc2)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -7728,11 +7728,11 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][&gt;]}{[&lt;][&gt;]OC(C)C[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -7746,11 +7746,11 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;],[&gt;]CC([&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}[H],[&gt;]C(C[&lt;])C(=O)OC{[&lt;][&gt;]COC[&lt;][&gt;]}{[&lt;][&gt;]COC[&lt;][&gt;]}[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D407" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -7764,11 +7764,11 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;],[&gt;]CC(C)(C(=O)OCCOC(=O)C(C)(C){[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]})[&lt;],[&gt;]C(C)(C(=O)OCCOC(=O)C(C)(C){[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]})C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -7782,11 +7782,11 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>[H]COCCO{[&lt;][&gt;]C(=O)CCCCCO[&lt;],[&gt;]C(CCCCCO[&lt;])OC{[&lt;][&gt;]COC[&lt;][&gt;]}[H][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="410">
@@ -7800,11 +7800,11 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;],[&gt;]CC([&lt;])c(cc1)ccc1CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[H],[&gt;]C(C[&lt;])c(cc1)ccc1CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}N[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -7818,11 +7818,11 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;],[&gt;]CC([&lt;])c(cc1)ccc1CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}C(=O)O[H],[&gt;]C(C[&lt;])c(cc1)ccc1CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}C(=O)O[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
@@ -7836,11 +7836,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;],[&gt;]CC([&lt;])c(cc1)ccc1CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}S[H],[&gt;]C(C[&lt;])c(cc1)ccc1CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}{[&lt;][&gt;]OCC[&lt;][&gt;]}S[H][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C(=O)OCC(CC4C5)(CC65)CC(C4)C6)(C)[&lt;],[&gt;]C(C(=O)OCC(CC1C2)(CC32)CC(C1)C3)(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -7872,11 +7872,11 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;],[&gt;]CC([&lt;])c(ccc1)cc1C{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Br,[&gt;]C(C[&lt;])c(ccc1)cc1C{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Br[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
@@ -7890,11 +7890,11 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>[H]NCC(C)(C){[&lt;][&gt;]CC(C(=O)OCCO)([&lt;])COC(=O)C(C){[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Cl,[&gt;]C(C(=O)OCCO)(C[&lt;])COC(=O)C(C){[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Cl[&gt;]}C(c(cc1)ccc1)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
@@ -7908,11 +7908,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>{[][&gt;]N=Cc(cc1)ccc1C=NCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -7926,11 +7926,11 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>{[][&gt;4]C(=O)Nc(cc2)ccc2Cc(cc1)ccc1NC(=O)[&lt;3],[&gt;4]C(=O)Nc(cc2)ccc2Cc(cc1)ccc1NC(=O)[&lt;1],[&gt;3]NCCC[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCN[&lt;1],[&gt;3]NCCC[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCN[&lt;4][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -7944,11 +7944,11 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>{[][&gt;4]C(=O)NC(CC2)CCC2CC(CC1)CCC1NC(=O)[&lt;3],[&gt;4]C(=O)NC(CC2)CCC2CC(CC1)CCC1NC(=O)[&lt;1],[&gt;3]NNC(=O)C(=O)NCCC[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCNC(=O)C(=O)NN[&lt;1],[&gt;3]NNC(=O)C(=O)NCCC[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCNC(=O)C(=O)NN[&lt;4][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -7962,11 +7962,11 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>{[][&gt;4]C(=O)NC(CC2)CCC2CC(CC1)CCC1NC(=O)[&lt;3],[&gt;4]C(=O)NC(CC2)CCC2CC(CC1)CCC1NC(=O)[&lt;1],[&gt;3]NCCC[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCN[&lt;1],[&gt;3]NCCC[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCN[&lt;4][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
@@ -7980,11 +7980,11 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;2]OCC[&lt;2],[&gt;3]C(=O)Nc(ccc1C)cc1NC(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)Nc(c(c2)C)cc(c2)NC(=O)[&lt;2],[&gt;4]OCCCO[&lt;3],[&gt;3]C(=O)Nc(ccc1C)cc1NC(=O)[&lt;4],[&gt;3]C(=O)Nc(c(c2)C)cc(c2)NC(=O)[&lt;4],[&gt;4]OCCCO[&lt;1],[&gt;3]C(=O)Nc(ccc1C)cc1NC(=O)[&lt;1],[&gt;3]C(=O)Nc(c(c2)C)cc(c2)NC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -7998,11 +7998,11 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]COC[&lt;][&gt;]}C(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="422">
@@ -8016,11 +8016,11 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>[H]C{[&lt;][&gt;]OCC[&lt;][&gt;]}n(nn4)cc4c(cc(c(nn1)cn1CC{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}CCC[H])c2)cc2CO{[&lt;][&gt;]C(=C)CCCCCO[&lt;][&gt;]}C(=O)CCCCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -8034,11 +8034,11 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}OCC(CC)(CO{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}[H])COCc(nn1)cn1CCCCCCOC(=O){[&lt;][&gt;]N(CCCCCC)C(=O)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
@@ -8052,11 +8052,11 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]CCCCC(=O)OC[&lt;][&gt;]}C(CO{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}[H])COCc(nn1)cn1CCCCCCOC(=O){[&lt;][&gt;]N(CCCCCC)C(=O)[&lt;][&gt;]}C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425">
@@ -8070,11 +8070,11 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>[H]OC{[&lt;][&gt;]CCCCC(=O)OC[&lt;][&gt;]}C(CO{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}[H])(CO{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}[H])CO{[&lt;][&gt;]C(=O)CCCCCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -8088,11 +8088,11 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>[H]CC(Br)(C)C(=O)OC{[&lt;][&gt;]CCCCC(=O)OC[&lt;][&gt;]}C(COC(=O){[&lt;][&gt;]CCCCCOC(=O)[&lt;][&gt;]}C(Br)(C)C[H])(COC(=O){[&lt;][&gt;]CCCCCOC(=O)[&lt;][&gt;]}C(Br)(C)C[H])COC(=O){[&lt;][&gt;]CCCCCOC(=O)[&lt;][&gt;]}C(Br)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="427">
@@ -8106,11 +8106,11 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>{[][&gt;2]CC[&lt;1],[&gt;2]CCOC(=O)CCC[&lt;2],[&gt;3]OC(=O)C(C)(C)OC(=O)CCC[&lt;2],[&gt;3]CC(C)(C(OCCOCCOC)=O)[&lt;3],[&gt;3]C(C)(C(OCCOCCOC)=O)C[&lt;3],[&gt;3]C(C)(C(OCCOCCOC)=O)COC(=O)C(C)(C)[&lt;1],[&gt;3]CC(C)(C(OCCOCCOC)=O)OC(=O)C(C)(C)[&lt;1],[&gt;4]CC(C[&lt;8])(C[&lt;3])C[&lt;3],[&gt;4]CC(C)(C(OCCOCCOC)=O)[&lt;4],[&gt;4]C(C)(C(OCCOCCOC)=O)C[&lt;4],[&gt;4]CC(COC(=O)C(C)(C)[&lt;1])(C[&lt;3])C[&lt;3],[&gt;4]CC(COC(=O)C(C)(C)[&lt;1])(C[&lt;8])C[&lt;3],[&gt;4]CC(COC(=O)C(C)(C)Br)(C[&lt;3])C[&lt;3],[&gt;4]CC(COC(=O)C(C)(C)Br)(C[&lt;8])C[&lt;3],[&gt;4]CC(COC(=O)C(C)(C)[&lt;1])(COC(=O)C(C)(C)[&lt;1])C[&lt;3],[&gt;4]CC(Br)(COC(=O)C(C)(C)Br)C[&lt;3],[&gt;4]CC(Br)(COC(=O)C(C)(C)Br)C[&lt;3],[&gt;4]CC(COC(=O)C(C)(C)Br)(COC(=O)C(C)(C)[&lt;1])C[&lt;3],[&gt;4]CC(COC(=O)C(C)(C)[&lt;1])(COC(=O)C(C)(C)[&lt;1])C[&lt;8],[&gt;4]CC(COC(=O)C(C)(C)Br)(COC(=O)C(C)(C)Br)C[&lt;8],[&gt;4]CC(COC(=O)C(C)(C)[&lt;1])(COC(=O)C(C)(C)[&lt;1])COC(=O)C(C)(C)[&lt;1],[&gt;4]CC(COC(=O)C(C)(C)[&lt;1])(Br)COC(=O)C(C)(C)Br,[&gt;4]CC(COC(=O)C(C)(C)Br)(COC(=O)C(C)(C)Br)COC(=O)C(C)(C)[&lt;1],[&gt;9]CC(C)(C(OCCOCCOC)=O)[&lt;9],[&gt;9]C(C)(C(OCCOCCOC)=O)C[&lt;9],[&gt;8]CCCCCC(=O)OOC(=O)C(C)(C)[&lt;1],[&gt;8]CCCCCC(=O)O[&lt;8],[&gt;8]OC(=O)C(C)(C){[&lt;][&gt;]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;][&gt;]}[&lt;9],[&gt;1]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;1],[&gt;1]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;1];Br{[&lt;][&gt;]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CCCCCC(=O)O[&lt;][&gt;]}C(C)(C)C(=O)O[&lt;4],[&gt;2]CCBr,[&gt;2]CCBr,[&gt;3]C(C)(C(OCCOCCOC)=O)COC(=O)C(C)(C)Br,[&gt;3]CC(C)(C(OCCOCCOC)=O)OC(=O)C(C)(C)Br,[&gt;4]CC(COC(=O)C(C)(C)Br)(Br)COC(=O)C(C)(C)Br,[&gt;9]C(C)(C(OCCOCCOC)=O)CBr,[&gt;9]CC(C)(C(OCCOCCOC)=O)Br,[&gt;8]CCCCCC(=O)OOC(=O)C(C)(C)Br,[&gt;1]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)CBr,[&gt;1]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)Br[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>153</v>
+        <v>26</v>
       </c>
     </row>
     <row r="428">
@@ -8124,11 +8124,11 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Br{[&lt;][&gt;]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]OC(=O)CCCCC[&lt;][&gt;]}C(C)(C)C(=O)O{[&lt;][&gt;]CC(C)(C(OCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOC)=O)C[&lt;][&gt;]}CC(COC(=O){[&lt;][&gt;]CCCCCOC(=O)[&lt;][&gt;]}C(C)(C){[&lt;][&gt;]CC(C)(C(OCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;][&gt;]}Br)(COC(=O){[&lt;][&gt;]CCCCCOC(=O)[&lt;][&gt;]}C(C)(C){[&lt;][&gt;]CC(C)(C(OCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;][&gt;]}Br)COC(=O){[&lt;][&gt;]CCCCCOC(=O)[&lt;][&gt;]}C(C)(C){[&lt;][&gt;]CC(C)(C(OCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)[&lt;],[&gt;]C(C)(C(OCCOCCOCCOCCOCCOCCOCCOCCOCCOC)=O)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
     </row>
     <row r="429">
@@ -8142,11 +8142,11 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>[H]N{[&lt;][&gt;]C(CCCCN)C(=O)N[&lt;][&gt;]}CCCN(CCCN(CCCCN(CCCN(N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN(N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCN(CCCN(N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN(N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])N(CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H])CCCN{[&lt;][&gt;]C(=O)C(CCCCN)N[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
     </row>
     <row r="430">
@@ -8160,11 +8160,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(nn4)cn4[&lt;1],[&gt;3]COCC(COC[&lt;2])(COC[&lt;2])COC[&lt;2],[&gt;4]n(nn2)cc2[&lt;3],[&gt;2]c(nn1)cn1[&lt;6],[&gt;4]n(nn8)cc8[&lt;1],[&gt;3]COCC(COC[&lt;1])(COC[&lt;1])COC[&lt;1],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;4],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -8178,11 +8178,11 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>{[][&gt;2]c(nn4)cn4[&lt;1],[&gt;3]COCC(C)(COC[&lt;2])COC[&lt;2],[&gt;4]n(nn2)cc2[&lt;3],[&gt;2]c(nn1)cn1[&lt;6],[&gt;4]n(nn8)cc8[&lt;1],[&gt;3]COCC(C)(COC[&lt;1])COC[&lt;1],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;4],[&gt;6]CCCCC(C)(C)C(=O)O{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C(C)(C)CCCC[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -8196,11 +8196,11 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>{[][&gt;4]OC(=O)C(C(=O)O[&lt;3])C(=O)O[&lt;3],[&gt;4]OC(=O)C(C(=O)O[&lt;1])C(=O)O[&lt;1],[&gt;3]CC(O)COCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCOCC(O)C[&lt;1],[&gt;3]CC(O)COCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCOCC(O)C[&lt;4][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
@@ -8214,11 +8214,11 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>{[][&gt;4]NCCCOC{[&lt;][&gt;]COC[&lt;][&gt;]}C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CN[&lt;1])(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CN[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CN[&lt;1],[&gt;4]NCCCOC{[&lt;][&gt;]COC[&lt;][&gt;]}C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CN[&lt;7])(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CN[&lt;7])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CN[&lt;7],[&gt;7]C(=O)CCCOCOC{[&lt;][&gt;]COC[&lt;][&gt;]}C(COC{[&lt;][&gt;]COC[&lt;][&gt;]}OCCCC(=O)[&lt;4])(COC{[&lt;][&gt;]COC[&lt;][&gt;]}OCCCC(=O)[&lt;4])COC{[&lt;][&gt;]COC[&lt;][&gt;]}OCCCC(=O)[&lt;4],[&gt;7]C(=O)CCCOCOC{[&lt;][&gt;]COC[&lt;][&gt;]}C(COC{[&lt;][&gt;]COC[&lt;][&gt;]}OCCCC(=O)[&lt;1])(COC{[&lt;][&gt;]COC[&lt;][&gt;]}OCCCC(=O)[&lt;1])COC{[&lt;][&gt;]COC[&lt;][&gt;]}OCCCC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D433" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
     </row>
     <row r="434">
@@ -8232,11 +8232,11 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>{[][&gt;5]C(=O)CCCCCCC(=O)[&lt;4],[&gt;5]C(=O)CCCCCCC(=O)[&lt;1],[&gt;4]NCCOC{[&lt;][&gt;]COC[&lt;][&gt;]}C(OCC(OC(COC(C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COC(C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COC(C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;1],[&gt;4]NCCOC{[&lt;][&gt;]COC[&lt;][&gt;]}C(OCC(OC(COC(C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COC(C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COC(C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])C(COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5])COCC{[&lt;][&gt;]OCC[&lt;][&gt;]}N[&lt;5][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D434" t="n">
-        <v>317</v>
+        <v>169</v>
       </c>
     </row>
     <row r="435">
@@ -8250,11 +8250,11 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>{[][&gt;2]CC[&lt;1],[&gt;3]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;2],[&gt;4]CC[&lt;3],[&gt;5]SCCC(=O)OCC(CC)(COC(=O)CCS[&lt;4])COC(=O)CCS[&lt;4],[&gt;6]CC[&lt;5],[&gt;3]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;6],[&gt;3]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;6],[&gt;3]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;2],[&gt;5]SCCC(=O)OCC(CC)(COC(=O)CCS[&lt;2])COC(=O)CCS[&lt;2],[&gt;3]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;1],[&gt;3]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;1],[&gt;5]SCCC(=O)OCC(CC)(COC(=O)CCS[&lt;1])COC(=O)CCS[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D435" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>{[][&gt;2]CC[&lt;1],[&gt;3]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;2],[&gt;4]CC[&lt;3],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])OC(=O)CCS[&lt;4],[&gt;6]CC[&lt;5],[&gt;3]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;6],[&gt;3]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;6],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])OC(=O)CCS[&lt;4],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;4])(COC(=O)CCS[&lt;4])OC(=O)CCS[&lt;4],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;4])(COC(=O)CCS[&lt;4])OC(=O)CCS[&lt;2],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;4])(COC(=O)CCS[&lt;4])OC(=O)CCS[&lt;1],[&gt;5]SCCC(=O)OC(COC(=O)CCS[&lt;4])(COC(=O)CCS[&lt;4])COC(=O)CCS[&lt;4],[&gt;3]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;2],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])OC(=O)CCS[&lt;2],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])OC(=O)CCS[&lt;1],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])OC(=O)CCS[&lt;2],[&gt;5]SCCC(=O)OC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])COC(=O)CCS[&lt;2],[&gt;3]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;1],[&gt;3]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;1],[&gt;5]SCCC(=O)OCC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])OC(=O)CCS[&lt;1],[&gt;5]SCCC(=O)OC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])COC(=O)CCS[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -8286,11 +8286,11 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>{[][&gt;2]CC[&lt;1],[&gt;3]SCCCCCCS[&lt;2],[&gt;4]CC[&lt;3],[&gt;5]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;4],[&gt;6]CC[&lt;5],[&gt;3]SCCCCCCS[&lt;6],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])OC(=O)CCS[&lt;6],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])OC(=O)CCS[&lt;6],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;6])(COC(=O)CCS[&lt;6])OC(=O)CCS[&lt;6],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;6])(COC(=O)CCS[&lt;6])OC(=O)CCS[&lt;2],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;6])(COC(=O)CCS[&lt;6])OC(=O)CCS[&lt;1],[&gt;3]SCCC(=O)OC(COC(=O)CCS[&lt;6])(COC(=O)CCS[&lt;6])COC(=O)CCS[&lt;6],[&gt;5]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;4],[&gt;5]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;2],[&gt;5]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;2],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])OC(=O)CCS[&lt;2],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])OC(=O)CCS[&lt;1],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])OC(=O)CCS[&lt;2],[&gt;3]SCCC(=O)OC(COC(=O)CCS[&lt;2])(COC(=O)CCS[&lt;2])COC(=O)CCS[&lt;2],[&gt;3]SCCCCCCS[&lt;1],[&gt;5]CC(=O)OCc(cc1)cc([N+](=O)[O-])c1COC(=O)C[&lt;1],[&gt;5]CC(=O)OCc(c(c2)[N+](=O)[O-])ccc2COC(=O)C[&lt;1],[&gt;3]SCCC(=O)OCC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])OC(=O)CCS[&lt;1],[&gt;3]SCCC(=O)OC(COC(=O)CCS[&lt;1])(COC(=O)CCS[&lt;1])COC(=O)CCS[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -8304,11 +8304,11 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][&gt;]}C(=O)CCN(CCN(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -8322,11 +8322,11 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>{[][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][&gt;]}C(=O)CCN(CCN(CCN(N(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})N(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCN(N(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})N(CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]})CCC(=O){[&lt;][&gt;]NCCN(CCC(=O)[&lt;])CCC(=O)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="440">
@@ -8340,11 +8340,11 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>{[][&gt;]C(C[&lt;])[&lt;],[&gt;]CC([&lt;])[&lt;],[&gt;]CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
@@ -8358,11 +8358,11 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>[H]OB(O){[&lt;][&gt;]c(cc([&lt;])c1)cc1[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442">
@@ -8376,11 +8376,11 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCN([&lt;])[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -8394,11 +8394,11 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Br{[&lt;][&gt;]CCO[&lt;][&gt;]}C(C)C(=O)OCC(C)(C(=O)O{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}C(=O)C(C)(COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br)COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br)COC(=O)C(C){[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D443" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444">
@@ -8412,11 +8412,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}CCN({[&lt;][&gt;]OC(=O)C(C)OC(=O)C(C)[&lt;][&gt;]}Cc(cc1)ccc1C{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}N(CCO{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}[H])CCO{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}[H])CCO{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>82</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -8430,11 +8430,11 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Br{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc%16)ccc%16)C[&lt;][&gt;]}C(C)C(=O)Oc(cc8)ccc8C(c(cc4)ccc4)(O{[&lt;][&gt;]C(=O)CCCCC[&lt;][&gt;]}O[H])C(c(cc2)ccc2)(O{[&lt;][&gt;]C(=O)CCCCC[&lt;][&gt;]}O[H])c(cc1)ccc1OC(=O)C(C){[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D445" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="446">
@@ -8448,11 +8448,11 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Br{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc%16)ccc%16)C[&lt;][&gt;]}C(C)C(=O)Oc(cc8)ccc8C(c(cc4)ccc4)(O{[&lt;][&gt;]C(=O)CCCCC[&lt;][&gt;]}{[&lt;][&gt;]C(=O)CCCCC[&lt;][&gt;]}O[H]){[&lt;][&gt;]CC(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C(OC(C)(C)C)=O)C[&lt;][&gt;]}C(c(cc2)ccc2)(O{[&lt;][&gt;]C(=O)CCCCC[&lt;][&gt;]}O[H])c(cc1)ccc1OC(=O)C(C){[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -8466,11 +8466,11 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>[H]CCOC(C)OCC(O)CC(c(cc1)ccc1)C{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}CCCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -8484,11 +8484,11 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>[H]CCCC{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc4)ccc4)C[&lt;][&gt;]}CC(c(cc2)ccc2)CC(COC(OCC)C)O{[&lt;][&gt;]OCC[&lt;][&gt;]}CCOCc(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -8502,11 +8502,11 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>[H]CCCC{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc4)ccc4)C[&lt;][&gt;]}CC(c(cc2)ccc2)CC(CO)O{[&lt;][&gt;]OCC[&lt;][&gt;]}CCOCc(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -8520,11 +8520,11 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>[H]CCCC{[&lt;][&gt;]CC(c(cc8)ccc8)[&lt;],[&gt;]C(c(cc4)ccc4)C[&lt;][&gt;]}CC(c(cc2)ccc2)CC(COC(C(C)(C)Br)=O)O{[&lt;][&gt;]OCC[&lt;][&gt;]}CCOCc(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -8538,11 +8538,11 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>[H]CCCC{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}CC(c(cc1)ccc1)CC(O{[&lt;][&gt;]OCC[&lt;][&gt;]}CCOCc(cc8)c(cc8)[H])COC(=O)C(C)(C){[&lt;][&gt;]CC(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C(OC(C)(C)C)=O)C[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -8556,11 +8556,11 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>[H]CCCC{[&lt;][&gt;]OCC[&lt;][&gt;]}CC(c(cc%16)ccc%16)CC(OC{[&lt;][&gt;]CC(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C(OC(C)(C)C)=O)C[&lt;][&gt;]}CCOCc(cc%16)c(cc%16)[H])COC(=O)C(C)(C){[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc%16)ccc%16)C[&lt;][&gt;]}C(C(OC(C)(C)C)=O)CC(c(cc%16)ccc%16)CC(c(cc8)ccc8)CC(c(cc4)ccc4)CC(c(cc2)ccc2)CC(C(OC(C)(C)C)=O){[&lt;][&gt;]CC(C(OC(C)(C)C)=O)[&lt;],[&gt;]C(C(OC(C)(C)C)=O)C[&lt;][&gt;]}C(C)(C)C(=O)OCC(OCCOC{[&lt;][&gt;]COC[&lt;][&gt;]}c(cc%16)c(cc%16)[H])CC(c(cc1)ccc1)C{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}CCCC[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D452" t="n">
-        <v>269</v>
+        <v>12</v>
       </c>
     </row>
     <row r="453">
@@ -8574,11 +8574,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>[H]OCCOCCO{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -8592,11 +8592,11 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>[H]OC(=O)C=CC(=O)OCCOCCO{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)C=CC(=O)O[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="455">
@@ -8610,11 +8610,11 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>[H]c(cc2)c(cc2)C(=S)SC(C(=O)O)CC(=O)OCCOCCO{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)CC(C(=O)O)SC(=S)c(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D455" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="456">
@@ -8628,11 +8628,11 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>[H]OCCOC(=O)C(SC(c(cc2)ccc2)=S)CC(=O)OCCOCCO{[&lt;][&gt;]CCO[&lt;][&gt;]}C(=O)CC(SC(c(cc1)ccc1)=S)C(=O)OCCO[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D456" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="457">
@@ -8646,11 +8646,11 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>[H]c(cc%16)c(cc%16)C(=S)S{[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc8)ccc8)C[&lt;][&gt;]}C(C(=O)OCCO)CC(=O)OCC{[&lt;][&gt;]CCO[&lt;][&gt;]}OCCOC(=O)CC(C(=O)OCCO){[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}SC(=S)c(cc1)c(cc1)[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D457" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -8664,11 +8664,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>[H]c(cc2)c(cc2)C(=S)S{[&lt;][&gt;]CC(c(cc4)ccc4)[&lt;],[&gt;]C(c(cc1)ccc1)C[&lt;][&gt;]}C(CC(=O)OCC{[&lt;][&gt;]CCO[&lt;][&gt;]}OCCOC(=O)CC({[&lt;][&gt;]CC(c(cc%16)ccc%16)[&lt;],[&gt;]C(c(cc%16)ccc%16)C[&lt;][&gt;]}SC(=S)c(cc8)c(cc8)[H])C(=O)OCCO{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}[H])C(=O)OCCO{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}{[&lt;][&gt;]C(=O)C(C)OC(=O)C(C)O[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
     </row>
     <row r="459">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)CC(C)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
@@ -8700,11 +8700,11 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)CC(C)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461">
@@ -8718,11 +8718,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)CC(C)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -8736,11 +8736,11 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(Cl)C(Cl)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -8754,11 +8754,11 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>[H]{[&lt;][&gt;]C(=O)OCC(C)(C(OCCOC)=O)CO[&lt;][&gt;]}OCCCCCCOc(cc4)ccc4C(=O)Oc(c(c2)C)ccc2OC(=O)c(cc1)ccc1OCCCCCCO{[&lt;][&gt;]C(=O)OCC(C)(C(OCCOC)=O)CO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -8772,11 +8772,11 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>{[][&gt;1]CCO[&lt;1],[&gt;2]c(cc3)cc(c3-c3cc4)C(CCC[N+](C)(C)C)(CCC[N+](C)(C)C)c3cc4c(cc7)cc(c7-c7cc8)C(c7cc8[&lt;1])([&lt;2])[&lt;1],[&gt;2]c(cc3)cc(c3-c3cc4)C(CCC[N+](C)(C)C)(CCC[N+](C)(C)C)c3cc4c(cc%15)cc(c%15-c%15cc%16)C(c%15cc%16[&lt;1])([&lt;1])[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -8790,11 +8790,11 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>[H]CCCC[Si](C)(C)O[Si](C)(C){[&lt;][&gt;]O[Si](C)(C)[&lt;][&gt;]}CCCOC(=O)C(=C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -8808,11 +8808,11 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(cc(OCCCCCCC)c8)cc8C#Cc(cc4)ccc4C#C[Pt](P(c(cc2)ccc2)(c(cc2)ccc2)c(cc2)ccc2)(P(c(cc2)ccc2)(c(cc2)ccc2)c(cc2)ccc2)C#Cc(cc1)ccc1C#C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">
@@ -8826,11 +8826,11 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(cc2CCCCCC)sc2c(cc1CCCCCC)sc1[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
@@ -8844,11 +8844,11 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>[H]CCOP(=O)(OCC)C(C(C)(C)C)N(C(C)(C)C)O{[&lt;][&gt;]CC(C(=O)O)[&lt;],[&gt;]C(C(=O)O)C[&lt;],[&gt;]CC(c(cc1)ccc1)[&lt;],[&gt;]C(c(cc2)ccc2)C[&lt;][&gt;]}C(C(=O)O)(C)C[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="469">
@@ -8862,11 +8862,11 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC[&lt;],[&gt;]CC(CC)[&lt;],[&gt;]C(CC)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="470">
@@ -8880,11 +8880,11 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)CCCCC(=O)[&lt;1],[&gt;3]NCCCCCCN[&lt;2],[&gt;2]C(=O)CCCCC(=O)[&lt;3],[&gt;3]NCCCCCCN[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -8898,11 +8898,11 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC[&lt;],[&gt;]CC(CC)[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -8916,11 +8916,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC[&lt;],[&gt;]C(C[&lt;])C[&lt;],[&gt;]CC(C[&lt;])[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -8934,11 +8934,11 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>{[][&gt;]c(cn1[&lt;])c(c1)[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -8952,11 +8952,11 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>{[][&gt;]CCN([&lt;])[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -8970,11 +8970,11 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>[H]O{[&lt;][&gt;]CCO[&lt;][&gt;]}[H]</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
@@ -8988,11 +8988,11 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC=CC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -9006,11 +9006,11 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -9024,11 +9024,11 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479">
@@ -9042,11 +9042,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>{[][&gt;2]C(=O)C(=O)[&lt;1],[&gt;3]OCC(CO[&lt;2])(CO[&lt;2])CO[&lt;2],[&gt;2]C(=O)C(=O)[&lt;3],[&gt;3]OCC(CO[&lt;1])(CO[&lt;1])CO[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -9060,11 +9060,11 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>{[][&gt;2]CC=CC[&lt;2],[&gt;2]CC([&lt;3])C([&lt;3])C[&lt;2],[&gt;3]C(C[&lt;2])C([&lt;3])C[&lt;2],[&gt;3]SS[&lt;3],[&gt;3][&lt;2],[&gt;2][&lt;3],[&gt;2]CC(C([&lt;3])[&lt;3]),[&gt;2]CC([&lt;3])C(C[&lt;2]),[&gt;3]C(C[&lt;2])C(C[&lt;2]),[&gt;3]C(C[&lt;2])C(C),[&gt;3]C(C[&lt;2])C([&lt;3])C,[&gt;3]C(C)C([&lt;3])C,[&gt;3]C(C)C([&lt;3])C[&lt;2],[&gt;2]CC(C(C[&lt;2])C[&lt;2]),[&gt;3]C(C)C(C),[&gt;2]CC(C(C)C)[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481">
@@ -9078,11 +9078,11 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>{[][&gt;2]OCCO[&lt;1],[&gt;2]OCC[&lt;2],[&gt;3]C(=O)Nc(ccc1C)cc1NC(=O)[&lt;2],[&gt;2]OCCO[&lt;3],[&gt;3]C(=O)Nc(c(c2)C)cc(c2)NC(=O)[&lt;2],[&gt;4]OCCCO[&lt;3],[&gt;3]C(=O)Nc(ccc1C)cc1NC(=O)[&lt;4],[&gt;3]C(=O)Nc(c(c2)C)cc(c2)NC(=O)[&lt;4],[&gt;4]OCCCO[&lt;1],[&gt;3]C(=O)Nc(ccc1C)cc1NC(=O)[&lt;1],[&gt;3]C(=O)Nc(c(c2)C)cc(c2)NC(=O)[&lt;1][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -9096,11 +9096,11 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>{[][&gt;]CC(C)(C)[&lt;],[&gt;]C(C)(C)C[&lt;],[&gt;]CC([&lt;])c(cc1)ccc1C{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Br,[&gt;]C(C[&lt;])c(cc1)ccc1C{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}{[&lt;][&gt;]CC(C)(C(OC)=O)[&lt;],[&gt;]C(C)(C(OC)=O)C[&lt;][&gt;]}Br[]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -9114,11 +9114,11 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>{[][&gt;]OCC[&lt;][&gt;]}OCC{[&lt;][&gt;]OC(C)C[&lt;][]}</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D483" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484">
@@ -9132,11 +9132,11 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>[H]OB(O){[&lt;][&gt;]c(cc([&lt;])c1)cc1[&lt;][&gt;]}Br</t>
+          <t>ERROR: unsupported operand type(s) for +: 'NoneType' and 'str'</t>
         </is>
       </c>
       <c r="D484" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/polymercanon/Paper-Results/Excel/Validation/Duration.xlsx
+++ b/polymercanon/Paper-Results/Excel/Validation/Duration.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.420884</v>
+        <v>2.540212</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.399182</v>
+        <v>2.062394</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.903676</v>
+        <v>1.002813</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.320506</v>
+        <v>2.113124</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.165958</v>
+        <v>1.913819</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.369224</v>
+        <v>1.8537</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.092201</v>
+        <v>1.857275</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.894864</v>
+        <v>1.870685</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.08958</v>
+        <v>1.063854</v>
       </c>
     </row>
     <row r="11">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.950323</v>
+        <v>0.9364749999999999</v>
       </c>
     </row>
     <row r="12">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.149233</v>
+        <v>1.946483</v>
       </c>
     </row>
     <row r="13">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.947971</v>
+        <v>0.930752</v>
       </c>
     </row>
     <row r="14">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.051424</v>
+        <v>1.850674</v>
       </c>
     </row>
     <row r="15">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.25489</v>
+        <v>1.077604</v>
       </c>
     </row>
     <row r="16">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.075312</v>
+        <v>0.936472</v>
       </c>
     </row>
     <row r="17">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.249782</v>
+        <v>1.060095</v>
       </c>
     </row>
     <row r="18">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.083459</v>
+        <v>1.826435</v>
       </c>
     </row>
     <row r="19">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.055891</v>
+        <v>0.91271</v>
       </c>
     </row>
     <row r="20">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.011929</v>
+        <v>1.839085</v>
       </c>
     </row>
     <row r="21">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.13627</v>
+        <v>1.87199</v>
       </c>
     </row>
     <row r="22">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.205667</v>
+        <v>1.096624</v>
       </c>
     </row>
     <row r="23">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.110927</v>
+        <v>2.195468</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.959723</v>
+        <v>4.753158</v>
       </c>
     </row>
     <row r="25">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.15232</v>
+        <v>1.985473</v>
       </c>
     </row>
     <row r="26">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.404768</v>
+        <v>1.977471</v>
       </c>
     </row>
     <row r="27">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.076343</v>
+        <v>0.934898</v>
       </c>
     </row>
     <row r="28">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.13247</v>
+        <v>0.933802</v>
       </c>
     </row>
     <row r="29">
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.107093</v>
+        <v>0.93842</v>
       </c>
     </row>
     <row r="30">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.108031</v>
+        <v>0.932504</v>
       </c>
     </row>
     <row r="31">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.28709</v>
+        <v>1.995701</v>
       </c>
     </row>
     <row r="32">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.465391</v>
+        <v>1.24559</v>
       </c>
     </row>
     <row r="33">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.10466</v>
+        <v>0.993912</v>
       </c>
     </row>
     <row r="34">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.112807</v>
+        <v>1.935969</v>
       </c>
     </row>
     <row r="35">
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.067859</v>
+        <v>0.947823</v>
       </c>
     </row>
     <row r="36">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.018441</v>
+        <v>1.240941</v>
       </c>
     </row>
     <row r="37">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.747696</v>
+        <v>5.325455</v>
       </c>
     </row>
     <row r="38">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.830801</v>
+        <v>1.796009</v>
       </c>
     </row>
     <row r="39">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.996959</v>
+        <v>0.948561</v>
       </c>
     </row>
     <row r="40">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.961924</v>
+        <v>0.9135529999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.924516</v>
+        <v>0.903995</v>
       </c>
     </row>
     <row r="42">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.871621</v>
+        <v>1.852522</v>
       </c>
     </row>
     <row r="43">
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.947738</v>
+        <v>0.897628</v>
       </c>
     </row>
     <row r="44">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.120004</v>
+        <v>1.081162</v>
       </c>
     </row>
     <row r="45">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.996902</v>
+        <v>0.89646</v>
       </c>
     </row>
     <row r="46">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.025516</v>
+        <v>0.89461</v>
       </c>
     </row>
     <row r="47">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.176041</v>
+        <v>1.023651</v>
       </c>
     </row>
     <row r="48">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.228099</v>
+        <v>1.937263</v>
       </c>
     </row>
     <row r="49">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.913608</v>
+        <v>0.897226</v>
       </c>
     </row>
     <row r="50">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.540167</v>
+        <v>3.454429</v>
       </c>
     </row>
     <row r="51">
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.938323</v>
+        <v>0.898983</v>
       </c>
     </row>
     <row r="52">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.270979</v>
+        <v>0.903691</v>
       </c>
     </row>
     <row r="53">
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.067688</v>
+        <v>0.893102</v>
       </c>
     </row>
     <row r="54">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1.038661</v>
+        <v>0.891742</v>
       </c>
     </row>
     <row r="55">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3.379543</v>
+        <v>2.960144</v>
       </c>
     </row>
     <row r="56">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.908878</v>
+        <v>0.910767</v>
       </c>
     </row>
     <row r="57">
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.946945</v>
+        <v>0.913059</v>
       </c>
     </row>
     <row r="58">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1.890258</v>
+        <v>1.788722</v>
       </c>
     </row>
     <row r="59">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.067931</v>
+        <v>1.036048</v>
       </c>
     </row>
     <row r="60">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3.896832</v>
+        <v>3.590218</v>
       </c>
     </row>
     <row r="61">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.890849</v>
+        <v>1.726652</v>
       </c>
     </row>
     <row r="62">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.965363</v>
+        <v>0.882177</v>
       </c>
     </row>
     <row r="63">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.965605</v>
+        <v>0.923507</v>
       </c>
     </row>
     <row r="64">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.966258</v>
+        <v>0.940452</v>
       </c>
     </row>
     <row r="65">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1.170441</v>
+        <v>0.85725</v>
       </c>
     </row>
     <row r="66">
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.81597</v>
+        <v>0.985992</v>
       </c>
     </row>
     <row r="67">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2.34265</v>
+        <v>0.946345</v>
       </c>
     </row>
     <row r="68">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1.672997</v>
+        <v>1.010058</v>
       </c>
     </row>
     <row r="69">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.714016</v>
+        <v>2.078677</v>
       </c>
     </row>
     <row r="70">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.186434</v>
+        <v>0.842541</v>
       </c>
     </row>
     <row r="71">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1.227911</v>
+        <v>0.870887</v>
       </c>
     </row>
     <row r="72">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1.085834</v>
+        <v>0.876134</v>
       </c>
     </row>
     <row r="73">
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.415127</v>
+        <v>1.96074</v>
       </c>
     </row>
     <row r="74">
@@ -1537,7 +1537,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2.266202</v>
+        <v>1.786236</v>
       </c>
     </row>
     <row r="75">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2.328056</v>
+        <v>1.783128</v>
       </c>
     </row>
     <row r="76">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1.14784</v>
+        <v>0.883396</v>
       </c>
     </row>
     <row r="77">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.079672</v>
+        <v>0.894182</v>
       </c>
     </row>
     <row r="78">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.116936</v>
+        <v>0.900035</v>
       </c>
     </row>
     <row r="79">
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3.403441</v>
+        <v>2.887732</v>
       </c>
     </row>
     <row r="80">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.122561</v>
+        <v>0.91012</v>
       </c>
     </row>
     <row r="81">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>2.470225</v>
+        <v>2.006897</v>
       </c>
     </row>
     <row r="82">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1.20108</v>
+        <v>1.027486</v>
       </c>
     </row>
     <row r="83">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1.338256</v>
+        <v>1.080629</v>
       </c>
     </row>
     <row r="84">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1.165313</v>
+        <v>1.157104</v>
       </c>
     </row>
     <row r="85">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1.142862</v>
+        <v>1.125176</v>
       </c>
     </row>
     <row r="86">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>1.164819</v>
+        <v>1.109414</v>
       </c>
     </row>
     <row r="87">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.297838</v>
+        <v>1.168873</v>
       </c>
     </row>
     <row r="88">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1.226978</v>
+        <v>1.843121</v>
       </c>
     </row>
     <row r="89">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1.34451</v>
+        <v>1.954199</v>
       </c>
     </row>
     <row r="90">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>1.166502</v>
+        <v>1.34941</v>
       </c>
     </row>
     <row r="91">
@@ -1792,7 +1792,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1.207467</v>
+        <v>1.239143</v>
       </c>
     </row>
     <row r="92">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1.17992</v>
+        <v>1.305905</v>
       </c>
     </row>
     <row r="93">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1.373332</v>
+        <v>1.333044</v>
       </c>
     </row>
     <row r="94">
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1.153969</v>
+        <v>1.17001</v>
       </c>
     </row>
     <row r="95">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1.189973</v>
+        <v>1.047484</v>
       </c>
     </row>
     <row r="96">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1.175933</v>
+        <v>0.961988</v>
       </c>
     </row>
     <row r="97">
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1.161275</v>
+        <v>1.11828</v>
       </c>
     </row>
     <row r="98">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1.0869</v>
+        <v>1.162032</v>
       </c>
     </row>
     <row r="99">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1.167126</v>
+        <v>0.919594</v>
       </c>
     </row>
     <row r="100">
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1.230842</v>
+        <v>1.002347</v>
       </c>
     </row>
     <row r="101">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2.725779</v>
+        <v>2.058696</v>
       </c>
     </row>
     <row r="102">
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2.209679</v>
+        <v>1.866822</v>
       </c>
     </row>
     <row r="103">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>5.230849</v>
+        <v>4.560722</v>
       </c>
     </row>
     <row r="104">
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>1.070218</v>
+        <v>0.8579020000000001</v>
       </c>
     </row>
     <row r="105">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1.117051</v>
+        <v>0.911492</v>
       </c>
     </row>
     <row r="106">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2.261303</v>
+        <v>2.041284</v>
       </c>
     </row>
     <row r="107">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1.076172</v>
+        <v>0.936128</v>
       </c>
     </row>
     <row r="108">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>2.496422</v>
+        <v>2.284683</v>
       </c>
     </row>
     <row r="109">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>1.085635</v>
+        <v>1.019492</v>
       </c>
     </row>
     <row r="110">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2.179321</v>
+        <v>2.226039</v>
       </c>
     </row>
     <row r="111">
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2.096021</v>
+        <v>2.122497</v>
       </c>
     </row>
     <row r="112">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.965683</v>
+        <v>1.095538</v>
       </c>
     </row>
     <row r="113">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5.311844</v>
+        <v>5.631124</v>
       </c>
     </row>
     <row r="114">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.945882</v>
+        <v>0.974824</v>
       </c>
     </row>
     <row r="115">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.962982</v>
+        <v>1.034039</v>
       </c>
     </row>
     <row r="116">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1.054022</v>
+        <v>1.084013</v>
       </c>
     </row>
     <row r="117">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1.113672</v>
+        <v>1.078314</v>
       </c>
     </row>
     <row r="118">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1.057343</v>
+        <v>1.547566</v>
       </c>
     </row>
     <row r="119">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>2.223267</v>
+        <v>2.766963</v>
       </c>
     </row>
     <row r="120">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2.300633</v>
+        <v>2.224953</v>
       </c>
     </row>
     <row r="121">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2.152761</v>
+        <v>1.973105</v>
       </c>
     </row>
     <row r="122">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2.797516</v>
+        <v>2.949498</v>
       </c>
     </row>
     <row r="123">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1.023778</v>
+        <v>1.070133</v>
       </c>
     </row>
     <row r="124">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>2.714693</v>
+        <v>2.121925</v>
       </c>
     </row>
     <row r="125">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1.312988</v>
+        <v>1.015383</v>
       </c>
     </row>
     <row r="126">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1.501482</v>
+        <v>1.177924</v>
       </c>
     </row>
     <row r="127">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>2.332871</v>
+        <v>2.010633</v>
       </c>
     </row>
     <row r="128">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1.154888</v>
+        <v>1.059513</v>
       </c>
     </row>
     <row r="129">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2.182687</v>
+        <v>2.104129</v>
       </c>
     </row>
     <row r="130">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1.07995</v>
+        <v>1.030218</v>
       </c>
     </row>
     <row r="131">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4.496021</v>
+        <v>4.343193</v>
       </c>
     </row>
     <row r="132">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1.090714</v>
+        <v>1.03879</v>
       </c>
     </row>
     <row r="133">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.926324</v>
+        <v>1.022763</v>
       </c>
     </row>
     <row r="134">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1.936076</v>
+        <v>2.101183</v>
       </c>
     </row>
     <row r="135">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1.046167</v>
+        <v>1.014178</v>
       </c>
     </row>
     <row r="136">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1.022124</v>
+        <v>1.022631</v>
       </c>
     </row>
     <row r="137">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.969056</v>
+        <v>1.040675</v>
       </c>
     </row>
     <row r="138">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1.861324</v>
+        <v>2.128888</v>
       </c>
     </row>
     <row r="139">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>2.98423</v>
+        <v>3.637823</v>
       </c>
     </row>
     <row r="140">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1.104604</v>
+        <v>1.148799</v>
       </c>
     </row>
     <row r="141">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1.312219</v>
+        <v>1.077788</v>
       </c>
     </row>
     <row r="142">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>2.742532</v>
+        <v>3.192189</v>
       </c>
     </row>
     <row r="143">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1.19528</v>
+        <v>1.233956</v>
       </c>
     </row>
     <row r="144">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3.135464</v>
+        <v>2.995083</v>
       </c>
     </row>
     <row r="145">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.984283</v>
+        <v>1.036252</v>
       </c>
     </row>
     <row r="146">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.937438</v>
+        <v>1.224214</v>
       </c>
     </row>
     <row r="147">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.946695</v>
+        <v>1.150796</v>
       </c>
     </row>
     <row r="148">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.946399</v>
+        <v>1.526327</v>
       </c>
     </row>
     <row r="149">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1.006752</v>
+        <v>1.277815</v>
       </c>
     </row>
     <row r="150">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1.085013</v>
+        <v>1.383834</v>
       </c>
     </row>
     <row r="151">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1.184083</v>
+        <v>1.555477</v>
       </c>
     </row>
     <row r="152">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1.536599</v>
+        <v>1.376724</v>
       </c>
     </row>
     <row r="153">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1.998383</v>
+        <v>2.267289</v>
       </c>
     </row>
     <row r="154">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.935234</v>
+        <v>1.845216</v>
       </c>
     </row>
     <row r="155">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>2.039164</v>
+        <v>2.44876</v>
       </c>
     </row>
     <row r="156">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1.017597</v>
+        <v>1.085429</v>
       </c>
     </row>
     <row r="157">
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>1.041096</v>
+        <v>1.117752</v>
       </c>
     </row>
     <row r="158">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>1.028823</v>
+        <v>1.825972</v>
       </c>
     </row>
     <row r="159">
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>2.558015</v>
+        <v>2.761961</v>
       </c>
     </row>
     <row r="160">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1.156936</v>
+        <v>1.184377</v>
       </c>
     </row>
     <row r="161">
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>1.10557</v>
+        <v>1.488932</v>
       </c>
     </row>
     <row r="162">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>1.121004</v>
+        <v>1.63515</v>
       </c>
     </row>
     <row r="163">
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>1.034496</v>
+        <v>1.14942</v>
       </c>
     </row>
     <row r="164">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.994008</v>
+        <v>1.228851</v>
       </c>
     </row>
     <row r="165">
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.972423</v>
+        <v>1.422675</v>
       </c>
     </row>
     <row r="166">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>1.108902</v>
+        <v>1.779509</v>
       </c>
     </row>
     <row r="167">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>1.026969</v>
+        <v>1.496912</v>
       </c>
     </row>
     <row r="168">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3.802067</v>
+        <v>4.319114</v>
       </c>
     </row>
     <row r="169">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>0.982629</v>
+        <v>1.191456</v>
       </c>
     </row>
     <row r="170">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>1.003912</v>
+        <v>1.146659</v>
       </c>
     </row>
     <row r="171">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>1.01793</v>
+        <v>1.092684</v>
       </c>
     </row>
     <row r="172">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1.129728</v>
+        <v>1.280758</v>
       </c>
     </row>
     <row r="173">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3.482714</v>
+        <v>3.641221</v>
       </c>
     </row>
     <row r="174">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>1.062219</v>
+        <v>1.456375</v>
       </c>
     </row>
     <row r="175">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1.120275</v>
+        <v>1.333858</v>
       </c>
     </row>
     <row r="176">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>1.189735</v>
+        <v>1.234055</v>
       </c>
     </row>
     <row r="177">
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>1.14838</v>
+        <v>1.305506</v>
       </c>
     </row>
     <row r="178">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>1.125596</v>
+        <v>1.382508</v>
       </c>
     </row>
     <row r="179">
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>1.198517</v>
+        <v>1.698212</v>
       </c>
     </row>
     <row r="180">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>1.275638</v>
+        <v>1.660058</v>
       </c>
     </row>
     <row r="181">
@@ -3142,7 +3142,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>1.228631</v>
+        <v>1.639986</v>
       </c>
     </row>
     <row r="182">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>1.144422</v>
+        <v>1.50863</v>
       </c>
     </row>
     <row r="183">
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>1.150223</v>
+        <v>1.358801</v>
       </c>
     </row>
     <row r="184">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>1.080239</v>
+        <v>1.959388</v>
       </c>
     </row>
     <row r="185">
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>1.145112</v>
+        <v>1.513478</v>
       </c>
     </row>
     <row r="186">
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>2.431315</v>
+        <v>3.007717</v>
       </c>
     </row>
     <row r="187">
@@ -3232,7 +3232,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>1.101955</v>
+        <v>1.166638</v>
       </c>
     </row>
     <row r="188">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>1.195474</v>
+        <v>1.425622</v>
       </c>
     </row>
     <row r="189">
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>1.204467</v>
+        <v>2.987711</v>
       </c>
     </row>
     <row r="190">
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>1.190372</v>
+        <v>1.3863</v>
       </c>
     </row>
     <row r="191">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1.161542</v>
+        <v>1.134342</v>
       </c>
     </row>
     <row r="192">
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>1.00234</v>
+        <v>1.523292</v>
       </c>
     </row>
     <row r="193">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>0.951454</v>
+        <v>1.524738</v>
       </c>
     </row>
     <row r="194">
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>0.955767</v>
+        <v>1.214299</v>
       </c>
     </row>
     <row r="195">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>0.967116</v>
+        <v>1.211421</v>
       </c>
     </row>
     <row r="196">
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>1.044656</v>
+        <v>1.240599</v>
       </c>
     </row>
     <row r="197">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>1.099481</v>
+        <v>1.363758</v>
       </c>
     </row>
     <row r="198">
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>4.298143</v>
+        <v>7.044796</v>
       </c>
     </row>
     <row r="199">
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>2.550248</v>
+        <v>5.011187</v>
       </c>
     </row>
     <row r="200">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.933366</v>
+        <v>1.46649</v>
       </c>
     </row>
     <row r="201">
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>2.014117</v>
+        <v>3.062448</v>
       </c>
     </row>
     <row r="202">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>0.960719</v>
+        <v>2.043618</v>
       </c>
     </row>
     <row r="203">
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>0.960651</v>
+        <v>1.993265</v>
       </c>
     </row>
     <row r="204">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>2.649686</v>
+        <v>4.201737</v>
       </c>
     </row>
     <row r="205">
@@ -3502,7 +3502,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>0.983412</v>
+        <v>1.597743</v>
       </c>
     </row>
     <row r="206">
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>1.09656</v>
+        <v>1.610878</v>
       </c>
     </row>
     <row r="207">
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>1.274669</v>
+        <v>1.486024</v>
       </c>
     </row>
     <row r="208">
@@ -3547,7 +3547,7 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>1.216436</v>
+        <v>1.241186</v>
       </c>
     </row>
     <row r="209">
@@ -3562,7 +3562,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1.175977</v>
+        <v>1.256182</v>
       </c>
     </row>
     <row r="210">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>3.05667</v>
+        <v>2.962769</v>
       </c>
     </row>
     <row r="211">
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>3.041991</v>
+        <v>3.829999</v>
       </c>
     </row>
     <row r="212">
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>1.105079</v>
+        <v>1.48132</v>
       </c>
     </row>
     <row r="213">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>1.159966</v>
+        <v>1.142044</v>
       </c>
     </row>
     <row r="214">
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>4.184268</v>
+        <v>4.821524</v>
       </c>
     </row>
     <row r="215">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>4.06745</v>
+        <v>5.598147</v>
       </c>
     </row>
     <row r="216">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>2.808546</v>
+        <v>3.58323</v>
       </c>
     </row>
     <row r="217">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>1.068553</v>
+        <v>1.223429</v>
       </c>
     </row>
     <row r="218">
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3.16201</v>
+        <v>3.179568</v>
       </c>
     </row>
     <row r="219">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>1.136514</v>
+        <v>1.444881</v>
       </c>
     </row>
     <row r="220">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.982425</v>
+        <v>1.814435</v>
       </c>
     </row>
     <row r="221">
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>2.889751</v>
+        <v>3.513057</v>
       </c>
     </row>
     <row r="222">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>2.846407</v>
+        <v>3.596919</v>
       </c>
     </row>
     <row r="223">
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1.333599</v>
+        <v>1.367786</v>
       </c>
     </row>
     <row r="224">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3.527102</v>
+        <v>4.471593</v>
       </c>
     </row>
     <row r="225">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0.9918439999999999</v>
+        <v>1.324237</v>
       </c>
     </row>
     <row r="226">
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>1.064513</v>
+        <v>1.153835</v>
       </c>
     </row>
     <row r="227">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>2.724967</v>
+        <v>3.067427</v>
       </c>
     </row>
     <row r="228">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>1.061941</v>
+        <v>1.126369</v>
       </c>
     </row>
     <row r="229">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>1.081692</v>
+        <v>1.084279</v>
       </c>
     </row>
     <row r="230">
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>1.178041</v>
+        <v>1.160181</v>
       </c>
     </row>
     <row r="231">
@@ -3892,7 +3892,7 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>1.137286</v>
+        <v>1.122025</v>
       </c>
     </row>
     <row r="232">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>1.68791</v>
+        <v>1.866078</v>
       </c>
     </row>
     <row r="233">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3.953234</v>
+        <v>3.721753</v>
       </c>
     </row>
     <row r="234">
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3.36298</v>
+        <v>2.939956</v>
       </c>
     </row>
     <row r="235">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3.14071</v>
+        <v>2.94925</v>
       </c>
     </row>
     <row r="236">
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3.340635</v>
+        <v>3.045017</v>
       </c>
     </row>
     <row r="237">
@@ -3982,7 +3982,7 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>1.903115</v>
+        <v>2.178672</v>
       </c>
     </row>
     <row r="238">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>2.674897</v>
+        <v>3.062546</v>
       </c>
     </row>
     <row r="239">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>2.787781</v>
+        <v>2.98988</v>
       </c>
     </row>
     <row r="240">
@@ -4027,7 +4027,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>3.006185</v>
+        <v>3.873997</v>
       </c>
     </row>
     <row r="241">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>1.05818</v>
+        <v>1.313033</v>
       </c>
     </row>
     <row r="242">
@@ -4057,7 +4057,7 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>1.052325</v>
+        <v>1.405388</v>
       </c>
     </row>
     <row r="243">
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>1.043511</v>
+        <v>1.059162</v>
       </c>
     </row>
     <row r="244">
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>2.704373</v>
+        <v>2.980982</v>
       </c>
     </row>
     <row r="245">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>0.986811</v>
+        <v>1.127129</v>
       </c>
     </row>
     <row r="246">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>0.989411</v>
+        <v>1.107845</v>
       </c>
     </row>
     <row r="247">
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>1.014861</v>
+        <v>1.077921</v>
       </c>
     </row>
     <row r="248">
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>3.106008</v>
+        <v>3.125091</v>
       </c>
     </row>
     <row r="249">
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>3.873862</v>
+        <v>3.928684</v>
       </c>
     </row>
     <row r="250">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>3.282642</v>
+        <v>3.820456</v>
       </c>
     </row>
     <row r="251">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>2.992369</v>
+        <v>4.030853</v>
       </c>
     </row>
     <row r="252">
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>2.876328</v>
+        <v>3.479725</v>
       </c>
     </row>
     <row r="253">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>2.90634</v>
+        <v>3.509865</v>
       </c>
     </row>
     <row r="254">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>3.181996</v>
+        <v>3.873721</v>
       </c>
     </row>
     <row r="255">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>3.32049</v>
+        <v>4.686197</v>
       </c>
     </row>
     <row r="256">
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>1.027177</v>
+        <v>1.269166</v>
       </c>
     </row>
     <row r="257">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>3.027666</v>
+        <v>3.164074</v>
       </c>
     </row>
     <row r="258">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>4.086121</v>
+        <v>4.80708</v>
       </c>
     </row>
     <row r="259">
@@ -4312,7 +4312,7 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>0.995366</v>
+        <v>1.131111</v>
       </c>
     </row>
     <row r="260">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>3.524731</v>
+        <v>3.645473</v>
       </c>
     </row>
     <row r="261">
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>2.057672</v>
+        <v>2.308147</v>
       </c>
     </row>
     <row r="262">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>3.452741</v>
+        <v>4.197827</v>
       </c>
     </row>
     <row r="263">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>4.647846</v>
+        <v>5.372355</v>
       </c>
     </row>
     <row r="264">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>4.439124</v>
+        <v>5.282188</v>
       </c>
     </row>
     <row r="265">
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2.034252</v>
+        <v>3.635368</v>
       </c>
     </row>
     <row r="266">
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>2.862243</v>
+        <v>4.203577</v>
       </c>
     </row>
     <row r="267">
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>3.147047</v>
+        <v>4.306506</v>
       </c>
     </row>
     <row r="268">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>3.53883</v>
+        <v>4.454996</v>
       </c>
     </row>
     <row r="269">
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>4.417555</v>
+        <v>4.451052</v>
       </c>
     </row>
     <row r="270">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>3.624219</v>
+        <v>3.475735</v>
       </c>
     </row>
     <row r="271">
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>3.048456</v>
+        <v>3.402872</v>
       </c>
     </row>
     <row r="272">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>4.267499</v>
+        <v>3.736602</v>
       </c>
     </row>
     <row r="273">
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>3.814132</v>
+        <v>2.914675</v>
       </c>
     </row>
     <row r="274">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2.784825</v>
+        <v>3.134445</v>
       </c>
     </row>
     <row r="275">
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>4.071677</v>
+        <v>4.946614</v>
       </c>
     </row>
     <row r="276">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>4.695022</v>
+        <v>4.072426</v>
       </c>
     </row>
     <row r="277">
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>3.09804</v>
+        <v>4.353686</v>
       </c>
     </row>
     <row r="278">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>4.316377</v>
+        <v>4.15919</v>
       </c>
     </row>
     <row r="279">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>3.408567</v>
+        <v>3.612996</v>
       </c>
     </row>
     <row r="280">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>3.669854</v>
+        <v>3.846347</v>
       </c>
     </row>
     <row r="281">
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>4.339824</v>
+        <v>4.691338</v>
       </c>
     </row>
     <row r="282">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3.074021</v>
+        <v>4.098</v>
       </c>
     </row>
     <row r="283">
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>3.857098</v>
+        <v>5.118705</v>
       </c>
     </row>
     <row r="284">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>3.629155</v>
+        <v>4.236281</v>
       </c>
     </row>
     <row r="285">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>4.422927</v>
+        <v>3.640321</v>
       </c>
     </row>
     <row r="286">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>4.285615</v>
+        <v>2.883291</v>
       </c>
     </row>
     <row r="287">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>3.328074</v>
+        <v>3.553457</v>
       </c>
     </row>
     <row r="288">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>3.306175</v>
+        <v>3.072265</v>
       </c>
     </row>
     <row r="289">
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3.013246</v>
+        <v>2.898041</v>
       </c>
     </row>
     <row r="290">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>4.581613</v>
+        <v>3.203595</v>
       </c>
     </row>
     <row r="291">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>3.914747</v>
+        <v>3.907119</v>
       </c>
     </row>
     <row r="292">
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>4.535532</v>
+        <v>3.053856</v>
       </c>
     </row>
     <row r="293">
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>4.73642</v>
+        <v>3.375103</v>
       </c>
     </row>
     <row r="294">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>4.305465</v>
+        <v>2.786691</v>
       </c>
     </row>
     <row r="295">
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>5.352288</v>
+        <v>3.234066</v>
       </c>
     </row>
     <row r="296">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>4.22771</v>
+        <v>3.301327</v>
       </c>
     </row>
     <row r="297">
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>2.779586</v>
+        <v>2.539187</v>
       </c>
     </row>
     <row r="298">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>2.799294</v>
+        <v>2.086757</v>
       </c>
     </row>
     <row r="299">
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>2.662681</v>
+        <v>2.657057</v>
       </c>
     </row>
     <row r="300">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>3.790024</v>
+        <v>2.022888</v>
       </c>
     </row>
     <row r="301">
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>6.351188</v>
+        <v>5.122408</v>
       </c>
     </row>
     <row r="302">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>6.481627</v>
+        <v>6.408195</v>
       </c>
     </row>
     <row r="303">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>2.720075</v>
+        <v>2.934805</v>
       </c>
     </row>
     <row r="304">
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>4.232589</v>
+        <v>4.41567</v>
       </c>
     </row>
     <row r="305">
@@ -5002,7 +5002,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>4.650513</v>
+        <v>2.890533</v>
       </c>
     </row>
     <row r="306">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>2.632555</v>
+        <v>2.358353</v>
       </c>
     </row>
     <row r="307">
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>3.406855</v>
+        <v>3.306512</v>
       </c>
     </row>
     <row r="308">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>2.545701</v>
+        <v>2.309819</v>
       </c>
     </row>
     <row r="309">
@@ -5062,7 +5062,7 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>2.85252</v>
+        <v>3.132663</v>
       </c>
     </row>
     <row r="310">
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>2.48245</v>
+        <v>1.888563</v>
       </c>
     </row>
     <row r="311">
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>2.493134</v>
+        <v>2.538528</v>
       </c>
     </row>
     <row r="312">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>2.217765</v>
+        <v>2.053292</v>
       </c>
     </row>
     <row r="313">
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>2.337666</v>
+        <v>2.805861</v>
       </c>
     </row>
     <row r="314">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>2.337031</v>
+        <v>2.313695</v>
       </c>
     </row>
     <row r="315">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>2.652999</v>
+        <v>2.443987</v>
       </c>
     </row>
     <row r="316">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>2.268009</v>
+        <v>2.200464</v>
       </c>
     </row>
     <row r="317">
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>2.32469</v>
+        <v>2.539999</v>
       </c>
     </row>
     <row r="318">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>2.38963</v>
+        <v>2.544613</v>
       </c>
     </row>
     <row r="319">
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>3.714587</v>
+        <v>3.968618</v>
       </c>
     </row>
     <row r="320">
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>6.623884</v>
+        <v>6.935082</v>
       </c>
     </row>
     <row r="321">
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>7.296221</v>
+        <v>6.62319</v>
       </c>
     </row>
     <row r="322">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>2.495842</v>
+        <v>2.560451</v>
       </c>
     </row>
     <row r="323">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>2.613298</v>
+        <v>2.82577</v>
       </c>
     </row>
     <row r="324">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>3.105589</v>
+        <v>3.331773</v>
       </c>
     </row>
     <row r="325">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>2.399265</v>
+        <v>2.886476</v>
       </c>
     </row>
     <row r="326">
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>5.366557</v>
+        <v>6.140255</v>
       </c>
     </row>
     <row r="327">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>2.921987</v>
+        <v>2.994919</v>
       </c>
     </row>
     <row r="328">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>2.348877</v>
+        <v>2.541746</v>
       </c>
     </row>
     <row r="329">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2.708958</v>
+        <v>2.995597</v>
       </c>
     </row>
     <row r="330">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>3.08704</v>
+        <v>2.033862</v>
       </c>
     </row>
     <row r="331">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>4.101943</v>
+        <v>2.863594</v>
       </c>
     </row>
     <row r="332">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>3.04132</v>
+        <v>3.819008</v>
       </c>
     </row>
     <row r="333">
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>3.390624</v>
+        <v>3.883187</v>
       </c>
     </row>
     <row r="334">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3.425679</v>
+        <v>5.571091</v>
       </c>
     </row>
     <row r="335">
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>2.361291</v>
+        <v>5.632111</v>
       </c>
     </row>
     <row r="336">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>4.52951</v>
+        <v>9.090614</v>
       </c>
     </row>
     <row r="337">
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>6.024158</v>
+        <v>11.539648</v>
       </c>
     </row>
     <row r="338">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>6.532882</v>
+        <v>8.223000000000001</v>
       </c>
     </row>
     <row r="339">
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>5.788042</v>
+        <v>8.525340999999999</v>
       </c>
     </row>
     <row r="340">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>4.45233</v>
+        <v>9.452271</v>
       </c>
     </row>
     <row r="341">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>5.658507</v>
+        <v>9.819761</v>
       </c>
     </row>
     <row r="342">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>6.045149</v>
+        <v>9.772465</v>
       </c>
     </row>
     <row r="343">
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>4.968778</v>
+        <v>8.684182</v>
       </c>
     </row>
     <row r="344">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>6.290025</v>
+        <v>7.492632</v>
       </c>
     </row>
     <row r="345">
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>3.557264</v>
+        <v>5.674656</v>
       </c>
     </row>
     <row r="346">
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>8.058306</v>
+        <v>8.92151</v>
       </c>
     </row>
     <row r="347">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>8.209991</v>
+        <v>8.88555</v>
       </c>
     </row>
     <row r="348">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="C348" t="n">
-        <v>3.580019</v>
+        <v>5.569749</v>
       </c>
     </row>
     <row r="349">
@@ -5662,7 +5662,7 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>7.590573</v>
+        <v>9.939851000000001</v>
       </c>
     </row>
     <row r="350">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="C350" t="n">
-        <v>5.205689</v>
+        <v>4.797726</v>
       </c>
     </row>
     <row r="351">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="C351" t="n">
-        <v>9.040493</v>
+        <v>10.212663</v>
       </c>
     </row>
     <row r="352">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="C352" t="n">
-        <v>5.823318</v>
+        <v>7.624549</v>
       </c>
     </row>
     <row r="353">
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="C353" t="n">
-        <v>6.369706</v>
+        <v>7.740978</v>
       </c>
     </row>
     <row r="354">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="C354" t="n">
-        <v>5.209959</v>
+        <v>7.322819</v>
       </c>
     </row>
     <row r="355">
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="C355" t="n">
-        <v>8.375544</v>
+        <v>10.393531</v>
       </c>
     </row>
     <row r="356">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>3.841665</v>
+        <v>3.928406</v>
       </c>
     </row>
     <row r="357">
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="C357" t="n">
-        <v>5.407725</v>
+        <v>5.130365</v>
       </c>
     </row>
     <row r="358">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>5.61471</v>
+        <v>7.077714</v>
       </c>
     </row>
     <row r="359">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>5.53682</v>
+        <v>7.185326</v>
       </c>
     </row>
     <row r="360">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>6.180947</v>
+        <v>8.231348000000001</v>
       </c>
     </row>
     <row r="361">
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>6.057812</v>
+        <v>9.473725</v>
       </c>
     </row>
     <row r="362">
@@ -5857,7 +5857,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>11.063019</v>
+        <v>13.652248</v>
       </c>
     </row>
     <row r="363">
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3.809301</v>
+        <v>8.326513</v>
       </c>
     </row>
     <row r="364">
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="C364" t="n">
-        <v>9.263697000000001</v>
+        <v>11.739174</v>
       </c>
     </row>
     <row r="365">
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="C365" t="n">
-        <v>4.341626</v>
+        <v>4.48339</v>
       </c>
     </row>
     <row r="366">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>5.814955</v>
+        <v>8.126097</v>
       </c>
     </row>
     <row r="367">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>5.501052</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="368">
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>5.867912</v>
+        <v>5.75597</v>
       </c>
     </row>
     <row r="369">
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>6.760854</v>
+        <v>6.762969</v>
       </c>
     </row>
     <row r="370">
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="C370" t="n">
-        <v>4.712713</v>
+        <v>7.319683</v>
       </c>
     </row>
     <row r="371">
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>5.186289</v>
+        <v>4.880736</v>
       </c>
     </row>
     <row r="372">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="C372" t="n">
-        <v>4.483385</v>
+        <v>4.675381</v>
       </c>
     </row>
     <row r="373">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="C373" t="n">
-        <v>3.903496</v>
+        <v>4.279105</v>
       </c>
     </row>
     <row r="374">
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="C374" t="n">
-        <v>5.8661</v>
+        <v>6.227313</v>
       </c>
     </row>
     <row r="375">
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="C375" t="n">
-        <v>6.692037</v>
+        <v>6.539006</v>
       </c>
     </row>
     <row r="376">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>5.037208</v>
+        <v>5.047729</v>
       </c>
     </row>
     <row r="377">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>5.323322</v>
+        <v>4.17548</v>
       </c>
     </row>
     <row r="378">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="C378" t="n">
-        <v>4.711548</v>
+        <v>5.000974</v>
       </c>
     </row>
     <row r="379">
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="C379" t="n">
-        <v>4.835855</v>
+        <v>5.698545</v>
       </c>
     </row>
     <row r="380">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="C380" t="n">
-        <v>4.967026</v>
+        <v>7.049686</v>
       </c>
     </row>
     <row r="381">
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="C381" t="n">
-        <v>5.034271</v>
+        <v>5.37385</v>
       </c>
     </row>
     <row r="382">
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="C382" t="n">
-        <v>5.59088</v>
+        <v>6.45607</v>
       </c>
     </row>
     <row r="383">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="C383" t="n">
-        <v>6.537778</v>
+        <v>8.428542</v>
       </c>
     </row>
     <row r="384">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>6.274525</v>
+        <v>6.215635</v>
       </c>
     </row>
     <row r="385">
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="C385" t="n">
-        <v>5.419138</v>
+        <v>4.9893</v>
       </c>
     </row>
     <row r="386">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="C386" t="n">
-        <v>5.569081</v>
+        <v>6.282899</v>
       </c>
     </row>
     <row r="387">
@@ -6232,7 +6232,7 @@
         </is>
       </c>
       <c r="C387" t="n">
-        <v>6.741311</v>
+        <v>7.433019</v>
       </c>
     </row>
     <row r="388">
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="C388" t="n">
-        <v>6.311398</v>
+        <v>6.151909</v>
       </c>
     </row>
     <row r="389">
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="C389" t="n">
-        <v>8.336385</v>
+        <v>9.92977</v>
       </c>
     </row>
     <row r="390">
@@ -6277,7 +6277,7 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>8.130483999999999</v>
+        <v>10.802098</v>
       </c>
     </row>
     <row r="391">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>9.794340999999999</v>
+        <v>10.561232</v>
       </c>
     </row>
     <row r="392">
@@ -6307,7 +6307,7 @@
         </is>
       </c>
       <c r="C392" t="n">
-        <v>9.705201000000001</v>
+        <v>9.905162000000001</v>
       </c>
     </row>
     <row r="393">
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="C393" t="n">
-        <v>7.149415</v>
+        <v>7.66373</v>
       </c>
     </row>
     <row r="394">
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>5.329266</v>
+        <v>6.511696</v>
       </c>
     </row>
     <row r="395">
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="C395" t="n">
-        <v>8.455527999999999</v>
+        <v>8.337672</v>
       </c>
     </row>
     <row r="396">
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="C396" t="n">
-        <v>6.00275</v>
+        <v>7.560264</v>
       </c>
     </row>
     <row r="397">
@@ -6382,7 +6382,7 @@
         </is>
       </c>
       <c r="C397" t="n">
-        <v>9.086223</v>
+        <v>9.984575</v>
       </c>
     </row>
     <row r="398">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="C398" t="n">
-        <v>8.783132999999999</v>
+        <v>9.796372</v>
       </c>
     </row>
     <row r="399">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="C399" t="n">
-        <v>12.038315</v>
+        <v>14.14126</v>
       </c>
     </row>
     <row r="400">
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>11.45874</v>
+        <v>14.310283</v>
       </c>
     </row>
     <row r="401">
@@ -6442,7 +6442,7 @@
         </is>
       </c>
       <c r="C401" t="n">
-        <v>27.483569</v>
+        <v>31.181401</v>
       </c>
     </row>
     <row r="402">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="C402" t="n">
-        <v>1456.329061</v>
+        <v>1544.604895</v>
       </c>
     </row>
     <row r="403">
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="C403" t="n">
-        <v>6.662397</v>
+        <v>6.837036</v>
       </c>
     </row>
     <row r="404">
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="C404" t="n">
-        <v>4.62789</v>
+        <v>4.421575</v>
       </c>
     </row>
     <row r="405">
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>4.418323</v>
+        <v>5.34193</v>
       </c>
     </row>
     <row r="406">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>7.682811</v>
+        <v>7.228783</v>
       </c>
     </row>
     <row r="407">
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="C407" t="n">
-        <v>1.470785</v>
+        <v>1.205062</v>
       </c>
     </row>
     <row r="408">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="C408" t="n">
-        <v>4.864242</v>
+        <v>3.822209</v>
       </c>
     </row>
     <row r="409">
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="C409" t="n">
-        <v>8.250792000000001</v>
+        <v>8.809290000000001</v>
       </c>
     </row>
     <row r="410">
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>1.707814</v>
+        <v>1.952537</v>
       </c>
     </row>
     <row r="411">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="C411" t="n">
-        <v>1.725194</v>
+        <v>2.01669</v>
       </c>
     </row>
     <row r="412">
@@ -6607,7 +6607,7 @@
         </is>
       </c>
       <c r="C412" t="n">
-        <v>1.717794</v>
+        <v>2.338755</v>
       </c>
     </row>
     <row r="413">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>1.010224</v>
+        <v>1.157474</v>
       </c>
     </row>
     <row r="414">
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>1.526854</v>
+        <v>1.642204</v>
       </c>
     </row>
     <row r="415">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3.278967</v>
+        <v>3.464696</v>
       </c>
     </row>
     <row r="416">
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>2.401413</v>
+        <v>2.560473</v>
       </c>
     </row>
     <row r="417">
@@ -6682,7 +6682,7 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>3.761241</v>
+        <v>4.147738</v>
       </c>
     </row>
     <row r="418">
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>5.119524</v>
+        <v>5.818908</v>
       </c>
     </row>
     <row r="419">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>3.834807</v>
+        <v>3.483534</v>
       </c>
     </row>
     <row r="420">
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>5.136405</v>
+        <v>5.838744</v>
       </c>
     </row>
     <row r="421">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>6.338972</v>
+        <v>7.106773</v>
       </c>
     </row>
     <row r="422">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>14.691412</v>
+        <v>15.689085</v>
       </c>
     </row>
     <row r="423">
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>15.093114</v>
+        <v>14.681969</v>
       </c>
     </row>
     <row r="424">
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>12.990126</v>
+        <v>13.868367</v>
       </c>
     </row>
     <row r="425">
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>7.120842</v>
+        <v>7.621157</v>
       </c>
     </row>
     <row r="426">
@@ -6817,7 +6817,7 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>10.248304</v>
+        <v>9.915331999999999</v>
       </c>
     </row>
     <row r="427">
@@ -6832,7 +6832,7 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>105.205027</v>
+        <v>91.119294</v>
       </c>
     </row>
     <row r="428">
@@ -6847,7 +6847,7 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>90.526439</v>
+        <v>78.328382</v>
       </c>
     </row>
     <row r="429">
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>35.889807</v>
+        <v>29.443926</v>
       </c>
     </row>
     <row r="430">
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>6.137144</v>
+        <v>5.345036</v>
       </c>
     </row>
     <row r="431">
@@ -6892,7 +6892,7 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>5.07678</v>
+        <v>4.801735</v>
       </c>
     </row>
     <row r="432">
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>4.866808</v>
+        <v>4.323849</v>
       </c>
     </row>
     <row r="433">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>31.906998</v>
+        <v>30.970733</v>
       </c>
     </row>
     <row r="434">
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>278.498922</v>
+        <v>225.677691</v>
       </c>
     </row>
     <row r="435">
@@ -6952,7 +6952,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>17.052352</v>
+        <v>8.783543</v>
       </c>
     </row>
     <row r="436">
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>35.073784</v>
+        <v>28.847097</v>
       </c>
     </row>
     <row r="437">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>42.602309</v>
+        <v>31.863495</v>
       </c>
     </row>
     <row r="438">
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>4.383657</v>
+        <v>3.780916</v>
       </c>
     </row>
     <row r="439">
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>4.292606</v>
+        <v>3.452534</v>
       </c>
     </row>
     <row r="440">
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>1.265571</v>
+        <v>1.005807</v>
       </c>
     </row>
     <row r="441">
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>1.007454</v>
+        <v>0.925682</v>
       </c>
     </row>
     <row r="442">
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>0.962102</v>
+        <v>0.88585</v>
       </c>
     </row>
     <row r="443">
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>33.431251</v>
+        <v>32.253284</v>
       </c>
     </row>
     <row r="444">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>55.30048</v>
+        <v>50.421247</v>
       </c>
     </row>
     <row r="445">
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>28.294674</v>
+        <v>26.625846</v>
       </c>
     </row>
     <row r="446">
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>37.496821</v>
+        <v>35.513564</v>
       </c>
     </row>
     <row r="447">
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>3.991472</v>
+        <v>3.584644</v>
       </c>
     </row>
     <row r="448">
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>9.351732</v>
+        <v>6.972945</v>
       </c>
     </row>
     <row r="449">
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>9.128792000000001</v>
+        <v>7.062105</v>
       </c>
     </row>
     <row r="450">
@@ -7177,7 +7177,7 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>7.871703</v>
+        <v>6.943417</v>
       </c>
     </row>
     <row r="451">
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>13.58626</v>
+        <v>12.204207</v>
       </c>
     </row>
     <row r="452">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>215.846348</v>
+        <v>187.632571</v>
       </c>
     </row>
     <row r="453">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>2.840906</v>
+        <v>2.813739</v>
       </c>
     </row>
     <row r="454">
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>3.206366</v>
+        <v>3.193633</v>
       </c>
     </row>
     <row r="455">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>5.352516</v>
+        <v>5.378687</v>
       </c>
     </row>
     <row r="456">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>7.527195</v>
+        <v>6.684612</v>
       </c>
     </row>
     <row r="457">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>7.476893</v>
+        <v>6.943435</v>
       </c>
     </row>
     <row r="458">
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>65.25912700000001</v>
+        <v>59.725389</v>
       </c>
     </row>
     <row r="459">
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>1.811688</v>
+        <v>1.597193</v>
       </c>
     </row>
     <row r="460">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>1.887658</v>
+        <v>1.790487</v>
       </c>
     </row>
     <row r="461">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>2.396597</v>
+        <v>1.820192</v>
       </c>
     </row>
     <row r="462">
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>2.687892</v>
+        <v>1.765982</v>
       </c>
     </row>
     <row r="463">
@@ -7372,7 +7372,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>15.566007</v>
+        <v>9.266838</v>
       </c>
     </row>
     <row r="464">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>4.088005</v>
+        <v>2.936486</v>
       </c>
     </row>
     <row r="465">
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>3.337713</v>
+        <v>2.584834</v>
       </c>
     </row>
     <row r="466">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>3.078075</v>
+        <v>2.512143</v>
       </c>
     </row>
     <row r="467">
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>2.413115</v>
+        <v>1.746168</v>
       </c>
     </row>
     <row r="468">
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>8.881475999999999</v>
+        <v>6.954161</v>
       </c>
     </row>
     <row r="469">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>1.266933</v>
+        <v>1.030951</v>
       </c>
     </row>
     <row r="470">
@@ -7477,7 +7477,7 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>4.085314</v>
+        <v>3.638022</v>
       </c>
     </row>
     <row r="471">
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>2.635271</v>
+        <v>2.066699</v>
       </c>
     </row>
     <row r="472">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>1.32453</v>
+        <v>1.083162</v>
       </c>
     </row>
     <row r="473">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>2.53769</v>
+        <v>1.815567</v>
       </c>
     </row>
     <row r="474">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>1.038562</v>
+        <v>0.915262</v>
       </c>
     </row>
     <row r="475">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>2.203122</v>
+        <v>1.940318</v>
       </c>
     </row>
     <row r="476">
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>1.042443</v>
+        <v>0.861884</v>
       </c>
     </row>
     <row r="477">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>2.139259</v>
+        <v>1.861616</v>
       </c>
     </row>
     <row r="478">
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>2.372812</v>
+        <v>1.809146</v>
       </c>
     </row>
     <row r="479">
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>3.155675</v>
+        <v>2.793983</v>
       </c>
     </row>
     <row r="480">
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>6.789012</v>
+        <v>6.09184</v>
       </c>
     </row>
     <row r="481">
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>5.458403</v>
+        <v>5.110103</v>
       </c>
     </row>
     <row r="482">
@@ -7657,7 +7657,7 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>1.461571</v>
+        <v>1.383194</v>
       </c>
     </row>
     <row r="483">
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>4.960796</v>
+        <v>4.904729</v>
       </c>
     </row>
     <row r="484">
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>2.021982</v>
+        <v>1.791092</v>
       </c>
     </row>
   </sheetData>
